--- a/research/traditional_assets/database/data/philippines/philippines_food_wholesalers.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_food_wholesalers.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="pse_ani" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.353</v>
+        <v>0.0464</v>
       </c>
       <c r="G2">
-        <v>0.05691222570532915</v>
+        <v>0.03539412673879443</v>
       </c>
       <c r="H2">
-        <v>0.05689655172413793</v>
+        <v>0.03539412673879443</v>
       </c>
       <c r="I2">
-        <v>-0.0003134796238244514</v>
+        <v>0.00170015455950541</v>
       </c>
       <c r="J2">
-        <v>-0.0003134796238244514</v>
+        <v>0.00170015455950541</v>
       </c>
       <c r="K2">
-        <v>-1.09</v>
+        <v>-1.48</v>
       </c>
       <c r="L2">
-        <v>-0.0170846394984326</v>
+        <v>-0.02287480680061824</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.17</v>
+        <v>0.896</v>
       </c>
       <c r="V2">
-        <v>0.008972392638036808</v>
+        <v>0.06446043165467626</v>
       </c>
       <c r="W2">
-        <v>-0.01971066907775769</v>
+        <v>-0.02851637764932563</v>
       </c>
       <c r="X2">
-        <v>0.08746974541320848</v>
+        <v>0.1029819068728733</v>
       </c>
       <c r="Y2">
-        <v>-0.1071804144909662</v>
+        <v>-0.1314982845221989</v>
       </c>
       <c r="Z2">
-        <v>0.9429779183540749</v>
+        <v>0.9993358355343436</v>
       </c>
       <c r="AA2">
-        <v>-0.0002956043631203997</v>
+        <v>0.001699025377260862</v>
       </c>
       <c r="AB2">
-        <v>0.08397232529639034</v>
+        <v>0.07977414790582404</v>
       </c>
       <c r="AC2">
-        <v>-0.08426792965951074</v>
+        <v>-0.07807512252856318</v>
       </c>
       <c r="AD2">
-        <v>14.7</v>
+        <v>13.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>14.7</v>
+        <v>13.4</v>
       </c>
       <c r="AG2">
-        <v>13.53</v>
+        <v>12.504</v>
       </c>
       <c r="AH2">
-        <v>0.1013094417643005</v>
+        <v>0.4908424908424908</v>
       </c>
       <c r="AI2">
-        <v>0.1657271702367531</v>
+        <v>0.169620253164557</v>
       </c>
       <c r="AJ2">
-        <v>0.09400402973667754</v>
+        <v>0.4735646114225117</v>
       </c>
       <c r="AK2">
-        <v>0.1545755740888838</v>
+        <v>0.1600942333299191</v>
       </c>
       <c r="AL2">
-        <v>0.896</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AM2">
-        <v>0.896</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AN2">
-        <v>21.875</v>
+        <v>10.80645161290323</v>
       </c>
       <c r="AO2">
-        <v>-0.02232142857142857</v>
+        <v>0.1170212765957447</v>
       </c>
       <c r="AP2">
-        <v>20.13392857142857</v>
+        <v>10.08387096774194</v>
       </c>
       <c r="AQ2">
-        <v>-0.02232142857142857</v>
+        <v>0.1170212765957447</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.353</v>
+        <v>0.0464</v>
       </c>
       <c r="G3">
-        <v>0.05691222570532915</v>
+        <v>0.03539412673879443</v>
       </c>
       <c r="H3">
-        <v>0.05689655172413793</v>
+        <v>0.03539412673879443</v>
       </c>
       <c r="I3">
-        <v>-0.0003134796238244514</v>
+        <v>0.00170015455950541</v>
       </c>
       <c r="J3">
-        <v>-0.0003134796238244514</v>
+        <v>0.00170015455950541</v>
       </c>
       <c r="K3">
-        <v>-1.09</v>
+        <v>-1.48</v>
       </c>
       <c r="L3">
-        <v>-0.0170846394984326</v>
+        <v>-0.02287480680061824</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +760,8845 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.17</v>
+        <v>0.896</v>
       </c>
       <c r="V3">
-        <v>0.008972392638036808</v>
+        <v>0.06446043165467626</v>
       </c>
       <c r="W3">
-        <v>-0.01971066907775769</v>
+        <v>-0.02851637764932563</v>
       </c>
       <c r="X3">
-        <v>0.08746974541320848</v>
+        <v>0.1029819068728733</v>
       </c>
       <c r="Y3">
-        <v>-0.1071804144909662</v>
+        <v>-0.1314982845221989</v>
       </c>
       <c r="Z3">
-        <v>0.9429779183540749</v>
+        <v>0.9993358355343436</v>
       </c>
       <c r="AA3">
-        <v>-0.0002956043631203997</v>
+        <v>0.001699025377260862</v>
       </c>
       <c r="AB3">
-        <v>0.08397232529639034</v>
+        <v>0.07977414790582404</v>
       </c>
       <c r="AC3">
-        <v>-0.08426792965951074</v>
+        <v>-0.07807512252856318</v>
       </c>
       <c r="AD3">
-        <v>14.7</v>
+        <v>13.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>14.7</v>
+        <v>13.4</v>
       </c>
       <c r="AG3">
-        <v>13.53</v>
+        <v>12.504</v>
       </c>
       <c r="AH3">
-        <v>0.1013094417643005</v>
+        <v>0.4908424908424908</v>
       </c>
       <c r="AI3">
-        <v>0.1657271702367531</v>
+        <v>0.169620253164557</v>
       </c>
       <c r="AJ3">
-        <v>0.09400402973667754</v>
+        <v>0.4735646114225117</v>
       </c>
       <c r="AK3">
-        <v>0.1545755740888838</v>
+        <v>0.1600942333299191</v>
       </c>
       <c r="AL3">
-        <v>0.896</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AM3">
-        <v>0.896</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AN3">
-        <v>21.875</v>
+        <v>10.80645161290323</v>
       </c>
       <c r="AO3">
-        <v>-0.02232142857142857</v>
+        <v>0.1170212765957447</v>
       </c>
       <c r="AP3">
-        <v>20.13392857142857</v>
+        <v>10.08387096774194</v>
       </c>
       <c r="AQ3">
-        <v>-0.02232142857142857</v>
+        <v>0.1170212765957447</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AgriNurture, Inc. (PSE:ANI)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PSE:ANI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Food Wholesalers</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.5106382978723401</v>
+      </c>
+      <c r="F2">
+        <v>4.58441846785003</v>
+      </c>
+      <c r="G2">
+        <v>10.8064516129032</v>
+      </c>
+      <c r="H2">
+        <v>5.94435483870968</v>
+      </c>
+      <c r="I2">
+        <v>0.490842490842491</v>
+      </c>
+      <c r="J2">
+        <v>0.27</v>
+      </c>
+      <c r="K2">
+        <v>13.9</v>
+      </c>
+      <c r="L2">
+        <v>24.8235296506121</v>
+      </c>
+      <c r="M2">
+        <v>26.404</v>
+      </c>
+      <c r="N2">
+        <v>31.2985296506121</v>
+      </c>
+      <c r="O2">
+        <v>13.4</v>
+      </c>
+      <c r="P2">
+        <v>7.371</v>
+      </c>
+      <c r="Q2">
+        <v>0.079774147905824</v>
+      </c>
+      <c r="R2">
+        <v>0.07336652479789001</v>
+      </c>
+      <c r="S2">
+        <v>0.0557004277832879</v>
+      </c>
+      <c r="T2">
+        <v>0.038175</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.102981906872873</v>
+      </c>
+      <c r="X2">
+        <v>0.0863825682162877</v>
+      </c>
+      <c r="Y2">
+        <v>0.869125413867768</v>
+      </c>
+      <c r="Z2">
+        <v>0.644343886132671</v>
+      </c>
+      <c r="AA2">
+        <v>13.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.07426723704438384</v>
+      </c>
+      <c r="AC2">
+        <v>0.5106382978723404</v>
+      </c>
+      <c r="AD2">
+        <v>13.4</v>
+      </c>
+      <c r="AE2">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AF2">
+        <v>0.76</v>
+      </c>
+      <c r="AG2">
+        <v>1.24</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>13.9</v>
+      </c>
+      <c r="AK2">
+        <v>0.07384654256887045</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.25</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>1.75</v>
+      </c>
+      <c r="AR2">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AS2">
+        <v>13.4</v>
+      </c>
+      <c r="AT2">
+        <v>0.896</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.07604962444813942</v>
+      </c>
+      <c r="C2">
+        <v>29.94008882864366</v>
+      </c>
+      <c r="D2">
+        <v>29.04408882864366</v>
+      </c>
+      <c r="E2">
+        <v>-13.4</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.896</v>
+      </c>
+      <c r="H2">
+        <v>13.9</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>2.48</v>
+      </c>
+      <c r="K2">
+        <v>0.76</v>
+      </c>
+      <c r="L2">
+        <v>1.72</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.72</v>
+      </c>
+      <c r="O2">
+        <v>0.43</v>
+      </c>
+      <c r="P2">
+        <v>1.29</v>
+      </c>
+      <c r="Q2">
+        <v>2.05</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.07604962444813942</v>
+      </c>
+      <c r="T2">
+        <v>0.5044193424952811</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.25</v>
+      </c>
+      <c r="W2">
+        <v>0.033525</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.07590375038701908</v>
+      </c>
+      <c r="C3">
+        <v>29.78127618557609</v>
+      </c>
+      <c r="D3">
+        <v>29.15827618557609</v>
+      </c>
+      <c r="E3">
+        <v>-13.127</v>
+      </c>
+      <c r="F3">
+        <v>0.273</v>
+      </c>
+      <c r="G3">
+        <v>0.896</v>
+      </c>
+      <c r="H3">
+        <v>13.9</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>2.48</v>
+      </c>
+      <c r="K3">
+        <v>0.76</v>
+      </c>
+      <c r="L3">
+        <v>1.72</v>
+      </c>
+      <c r="M3">
+        <v>0.0122031</v>
+      </c>
+      <c r="N3">
+        <v>1.7077969</v>
+      </c>
+      <c r="O3">
+        <v>0.426949225</v>
+      </c>
+      <c r="P3">
+        <v>1.280847675</v>
+      </c>
+      <c r="Q3">
+        <v>2.040847675</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.07633181857274654</v>
+      </c>
+      <c r="T3">
+        <v>0.5082407011505483</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.25</v>
+      </c>
+      <c r="W3">
+        <v>0.033525</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>140.9477919545033</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.07575787632589873</v>
+      </c>
+      <c r="C4">
+        <v>29.62336494568102</v>
+      </c>
+      <c r="D4">
+        <v>29.27336494568102</v>
+      </c>
+      <c r="E4">
+        <v>-12.854</v>
+      </c>
+      <c r="F4">
+        <v>0.546</v>
+      </c>
+      <c r="G4">
+        <v>0.896</v>
+      </c>
+      <c r="H4">
+        <v>13.9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>2.48</v>
+      </c>
+      <c r="K4">
+        <v>0.76</v>
+      </c>
+      <c r="L4">
+        <v>1.72</v>
+      </c>
+      <c r="M4">
+        <v>0.0244062</v>
+      </c>
+      <c r="N4">
+        <v>1.6955938</v>
+      </c>
+      <c r="O4">
+        <v>0.42389845</v>
+      </c>
+      <c r="P4">
+        <v>1.27169535</v>
+      </c>
+      <c r="Q4">
+        <v>2.03169535</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.07661977176112114</v>
+      </c>
+      <c r="T4">
+        <v>0.5121400467171476</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.25</v>
+      </c>
+      <c r="W4">
+        <v>0.033525</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>70.47389597725167</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.07561200226477836</v>
+      </c>
+      <c r="C5">
+        <v>29.4663658248663</v>
+      </c>
+      <c r="D5">
+        <v>29.3893658248663</v>
+      </c>
+      <c r="E5">
+        <v>-12.581</v>
+      </c>
+      <c r="F5">
+        <v>0.819</v>
+      </c>
+      <c r="G5">
+        <v>0.896</v>
+      </c>
+      <c r="H5">
+        <v>13.9</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>2.48</v>
+      </c>
+      <c r="K5">
+        <v>0.76</v>
+      </c>
+      <c r="L5">
+        <v>1.72</v>
+      </c>
+      <c r="M5">
+        <v>0.0366093</v>
+      </c>
+      <c r="N5">
+        <v>1.6833907</v>
+      </c>
+      <c r="O5">
+        <v>0.420847675</v>
+      </c>
+      <c r="P5">
+        <v>1.262543025</v>
+      </c>
+      <c r="Q5">
+        <v>2.022543025</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.0769136621286375</v>
+      </c>
+      <c r="T5">
+        <v>0.5161197911614087</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.25</v>
+      </c>
+      <c r="W5">
+        <v>0.033525</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>46.98259731816779</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.07546612820365803</v>
+      </c>
+      <c r="C6">
+        <v>29.31028970957025</v>
+      </c>
+      <c r="D6">
+        <v>29.50628970957024</v>
+      </c>
+      <c r="E6">
+        <v>-12.308</v>
+      </c>
+      <c r="F6">
+        <v>1.092</v>
+      </c>
+      <c r="G6">
+        <v>0.896</v>
+      </c>
+      <c r="H6">
+        <v>13.9</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>2.48</v>
+      </c>
+      <c r="K6">
+        <v>0.76</v>
+      </c>
+      <c r="L6">
+        <v>1.72</v>
+      </c>
+      <c r="M6">
+        <v>0.04881240000000001</v>
+      </c>
+      <c r="N6">
+        <v>1.6711876</v>
+      </c>
+      <c r="O6">
+        <v>0.4177969</v>
+      </c>
+      <c r="P6">
+        <v>1.2533907</v>
+      </c>
+      <c r="Q6">
+        <v>2.0133907</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.07721367521214378</v>
+      </c>
+      <c r="T6">
+        <v>0.5201824469482587</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.25</v>
+      </c>
+      <c r="W6">
+        <v>0.033525</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>35.23694798862584</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.07532025414253767</v>
+      </c>
+      <c r="C7">
+        <v>29.15514766016746</v>
+      </c>
+      <c r="D7">
+        <v>29.62414766016746</v>
+      </c>
+      <c r="E7">
+        <v>-12.035</v>
+      </c>
+      <c r="F7">
+        <v>1.365</v>
+      </c>
+      <c r="G7">
+        <v>0.896</v>
+      </c>
+      <c r="H7">
+        <v>13.9</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>2.48</v>
+      </c>
+      <c r="K7">
+        <v>0.76</v>
+      </c>
+      <c r="L7">
+        <v>1.72</v>
+      </c>
+      <c r="M7">
+        <v>0.06101550000000001</v>
+      </c>
+      <c r="N7">
+        <v>1.6589845</v>
+      </c>
+      <c r="O7">
+        <v>0.414746125</v>
+      </c>
+      <c r="P7">
+        <v>1.244238375</v>
+      </c>
+      <c r="Q7">
+        <v>2.004238375</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.07752000436056597</v>
+      </c>
+      <c r="T7">
+        <v>0.5243306323306212</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.25</v>
+      </c>
+      <c r="W7">
+        <v>0.033525</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>28.18955839090066</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.07517438008141733</v>
+      </c>
+      <c r="C8">
+        <v>29.00095091445645</v>
+      </c>
+      <c r="D8">
+        <v>29.74295091445645</v>
+      </c>
+      <c r="E8">
+        <v>-11.762</v>
+      </c>
+      <c r="F8">
+        <v>1.638</v>
+      </c>
+      <c r="G8">
+        <v>0.896</v>
+      </c>
+      <c r="H8">
+        <v>13.9</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>2.48</v>
+      </c>
+      <c r="K8">
+        <v>0.76</v>
+      </c>
+      <c r="L8">
+        <v>1.72</v>
+      </c>
+      <c r="M8">
+        <v>0.07321859999999999</v>
+      </c>
+      <c r="N8">
+        <v>1.6467814</v>
+      </c>
+      <c r="O8">
+        <v>0.41169535</v>
+      </c>
+      <c r="P8">
+        <v>1.23508605</v>
+      </c>
+      <c r="Q8">
+        <v>1.99508605</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.07783285115044397</v>
+      </c>
+      <c r="T8">
+        <v>0.5285670769764381</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.25</v>
+      </c>
+      <c r="W8">
+        <v>0.033525</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>23.4912986590839</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.07502850602029697</v>
+      </c>
+      <c r="C9">
+        <v>28.84771089123177</v>
+      </c>
+      <c r="D9">
+        <v>29.86271089123177</v>
+      </c>
+      <c r="E9">
+        <v>-11.489</v>
+      </c>
+      <c r="F9">
+        <v>1.911</v>
+      </c>
+      <c r="G9">
+        <v>0.896</v>
+      </c>
+      <c r="H9">
+        <v>13.9</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>2.48</v>
+      </c>
+      <c r="K9">
+        <v>0.76</v>
+      </c>
+      <c r="L9">
+        <v>1.72</v>
+      </c>
+      <c r="M9">
+        <v>0.08542170000000002</v>
+      </c>
+      <c r="N9">
+        <v>1.6345783</v>
+      </c>
+      <c r="O9">
+        <v>0.408644575</v>
+      </c>
+      <c r="P9">
+        <v>1.225933725</v>
+      </c>
+      <c r="Q9">
+        <v>1.985933725</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.07815242582827632</v>
+      </c>
+      <c r="T9">
+        <v>0.5328946279587243</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.25</v>
+      </c>
+      <c r="W9">
+        <v>0.033525</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>20.13539885064333</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.07488263195917665</v>
+      </c>
+      <c r="C10">
+        <v>28.69543919394247</v>
+      </c>
+      <c r="D10">
+        <v>29.98343919394247</v>
+      </c>
+      <c r="E10">
+        <v>-11.216</v>
+      </c>
+      <c r="F10">
+        <v>2.184</v>
+      </c>
+      <c r="G10">
+        <v>0.896</v>
+      </c>
+      <c r="H10">
+        <v>13.9</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>2.48</v>
+      </c>
+      <c r="K10">
+        <v>0.76</v>
+      </c>
+      <c r="L10">
+        <v>1.72</v>
+      </c>
+      <c r="M10">
+        <v>0.09762480000000001</v>
+      </c>
+      <c r="N10">
+        <v>1.6223752</v>
+      </c>
+      <c r="O10">
+        <v>0.4055938</v>
+      </c>
+      <c r="P10">
+        <v>1.2167814</v>
+      </c>
+      <c r="Q10">
+        <v>1.9767814</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.07847894778171374</v>
+      </c>
+      <c r="T10">
+        <v>0.5373162561362778</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.25</v>
+      </c>
+      <c r="W10">
+        <v>0.033525</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>17.61847399431292</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.07473675789805628</v>
+      </c>
+      <c r="C11">
+        <v>28.54414761444003</v>
+      </c>
+      <c r="D11">
+        <v>30.10514761444003</v>
+      </c>
+      <c r="E11">
+        <v>-10.943</v>
+      </c>
+      <c r="F11">
+        <v>2.457</v>
+      </c>
+      <c r="G11">
+        <v>0.896</v>
+      </c>
+      <c r="H11">
+        <v>13.9</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>2.48</v>
+      </c>
+      <c r="K11">
+        <v>0.76</v>
+      </c>
+      <c r="L11">
+        <v>1.72</v>
+      </c>
+      <c r="M11">
+        <v>0.1098279</v>
+      </c>
+      <c r="N11">
+        <v>1.6101721</v>
+      </c>
+      <c r="O11">
+        <v>0.402543025</v>
+      </c>
+      <c r="P11">
+        <v>1.207629075</v>
+      </c>
+      <c r="Q11">
+        <v>1.967629075</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.07881264604182009</v>
+      </c>
+      <c r="T11">
+        <v>0.5418350629550959</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.25</v>
+      </c>
+      <c r="W11">
+        <v>0.033525</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>15.66086577272259</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.07459088383693592</v>
+      </c>
+      <c r="C12">
+        <v>28.39384813681759</v>
+      </c>
+      <c r="D12">
+        <v>30.22784813681759</v>
+      </c>
+      <c r="E12">
+        <v>-10.67</v>
+      </c>
+      <c r="F12">
+        <v>2.73</v>
+      </c>
+      <c r="G12">
+        <v>0.896</v>
+      </c>
+      <c r="H12">
+        <v>13.9</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>2.48</v>
+      </c>
+      <c r="K12">
+        <v>0.76</v>
+      </c>
+      <c r="L12">
+        <v>1.72</v>
+      </c>
+      <c r="M12">
+        <v>0.122031</v>
+      </c>
+      <c r="N12">
+        <v>1.597969</v>
+      </c>
+      <c r="O12">
+        <v>0.39949225</v>
+      </c>
+      <c r="P12">
+        <v>1.19847675</v>
+      </c>
+      <c r="Q12">
+        <v>1.95847675</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.0791537598188177</v>
+      </c>
+      <c r="T12">
+        <v>0.5464542877032211</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.25</v>
+      </c>
+      <c r="W12">
+        <v>0.033525</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>14.09477919545033</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.0744450097758156</v>
+      </c>
+      <c r="C13">
+        <v>28.24455294134362</v>
+      </c>
+      <c r="D13">
+        <v>30.35155294134362</v>
+      </c>
+      <c r="E13">
+        <v>-10.397</v>
+      </c>
+      <c r="F13">
+        <v>3.003</v>
+      </c>
+      <c r="G13">
+        <v>0.896</v>
+      </c>
+      <c r="H13">
+        <v>13.9</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>2.48</v>
+      </c>
+      <c r="K13">
+        <v>0.76</v>
+      </c>
+      <c r="L13">
+        <v>1.72</v>
+      </c>
+      <c r="M13">
+        <v>0.1342341</v>
+      </c>
+      <c r="N13">
+        <v>1.5857659</v>
+      </c>
+      <c r="O13">
+        <v>0.396441475</v>
+      </c>
+      <c r="P13">
+        <v>1.189324425</v>
+      </c>
+      <c r="Q13">
+        <v>1.949324425</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.07950253907395011</v>
+      </c>
+      <c r="T13">
+        <v>0.5511773152546752</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.25</v>
+      </c>
+      <c r="W13">
+        <v>0.033525</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>12.81343563222758</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.07439813571469522</v>
+      </c>
+      <c r="C14">
+        <v>28.0115185327744</v>
+      </c>
+      <c r="D14">
+        <v>30.3915185327744</v>
+      </c>
+      <c r="E14">
+        <v>-10.124</v>
+      </c>
+      <c r="F14">
+        <v>3.276</v>
+      </c>
+      <c r="G14">
+        <v>0.896</v>
+      </c>
+      <c r="H14">
+        <v>13.9</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>2.48</v>
+      </c>
+      <c r="K14">
+        <v>0.76</v>
+      </c>
+      <c r="L14">
+        <v>1.72</v>
+      </c>
+      <c r="M14">
+        <v>0.1500408</v>
+      </c>
+      <c r="N14">
+        <v>1.5699592</v>
+      </c>
+      <c r="O14">
+        <v>0.3924898</v>
+      </c>
+      <c r="P14">
+        <v>1.1774694</v>
+      </c>
+      <c r="Q14">
+        <v>1.9374694</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.07985924513033549</v>
+      </c>
+      <c r="T14">
+        <v>0.5560076843413894</v>
+      </c>
+      <c r="U14">
+        <v>0.0458</v>
+      </c>
+      <c r="V14">
+        <v>0.25</v>
+      </c>
+      <c r="W14">
+        <v>0.03435</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>11.46354858145251</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.07426051165357489</v>
+      </c>
+      <c r="C15">
+        <v>27.85646957208696</v>
+      </c>
+      <c r="D15">
+        <v>30.50946957208696</v>
+      </c>
+      <c r="E15">
+        <v>-9.850999999999999</v>
+      </c>
+      <c r="F15">
+        <v>3.549</v>
+      </c>
+      <c r="G15">
+        <v>0.896</v>
+      </c>
+      <c r="H15">
+        <v>13.9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>2.48</v>
+      </c>
+      <c r="K15">
+        <v>0.76</v>
+      </c>
+      <c r="L15">
+        <v>1.72</v>
+      </c>
+      <c r="M15">
+        <v>0.1625442</v>
+      </c>
+      <c r="N15">
+        <v>1.5574558</v>
+      </c>
+      <c r="O15">
+        <v>0.38936395</v>
+      </c>
+      <c r="P15">
+        <v>1.16809185</v>
+      </c>
+      <c r="Q15">
+        <v>1.92809185</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08022415132594815</v>
+      </c>
+      <c r="T15">
+        <v>0.5609490963956143</v>
+      </c>
+      <c r="U15">
+        <v>0.0458</v>
+      </c>
+      <c r="V15">
+        <v>0.25</v>
+      </c>
+      <c r="W15">
+        <v>0.03435</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>10.58173715211001</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.07435388759245454</v>
+      </c>
+      <c r="C16">
+        <v>27.5033418966364</v>
+      </c>
+      <c r="D16">
+        <v>30.4293418966364</v>
+      </c>
+      <c r="E16">
+        <v>-9.577999999999999</v>
+      </c>
+      <c r="F16">
+        <v>3.822000000000001</v>
+      </c>
+      <c r="G16">
+        <v>0.896</v>
+      </c>
+      <c r="H16">
+        <v>13.9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>2.48</v>
+      </c>
+      <c r="K16">
+        <v>0.76</v>
+      </c>
+      <c r="L16">
+        <v>1.72</v>
+      </c>
+      <c r="M16">
+        <v>0.183456</v>
+      </c>
+      <c r="N16">
+        <v>1.536544</v>
+      </c>
+      <c r="O16">
+        <v>0.384136</v>
+      </c>
+      <c r="P16">
+        <v>1.152408</v>
+      </c>
+      <c r="Q16">
+        <v>1.912408</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08059754371215644</v>
+      </c>
+      <c r="T16">
+        <v>0.5660054250092398</v>
+      </c>
+      <c r="U16">
+        <v>0.048</v>
+      </c>
+      <c r="V16">
+        <v>0.25</v>
+      </c>
+      <c r="W16">
+        <v>0.036</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>9.375545089830801</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.07423276353133421</v>
+      </c>
+      <c r="C17">
+        <v>27.33436216207464</v>
+      </c>
+      <c r="D17">
+        <v>30.53336216207464</v>
+      </c>
+      <c r="E17">
+        <v>-9.305</v>
+      </c>
+      <c r="F17">
+        <v>4.095</v>
+      </c>
+      <c r="G17">
+        <v>0.896</v>
+      </c>
+      <c r="H17">
+        <v>13.9</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>2.48</v>
+      </c>
+      <c r="K17">
+        <v>0.76</v>
+      </c>
+      <c r="L17">
+        <v>1.72</v>
+      </c>
+      <c r="M17">
+        <v>0.19656</v>
+      </c>
+      <c r="N17">
+        <v>1.52344</v>
+      </c>
+      <c r="O17">
+        <v>0.38086</v>
+      </c>
+      <c r="P17">
+        <v>1.14258</v>
+      </c>
+      <c r="Q17">
+        <v>1.90258</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08097972180156965</v>
+      </c>
+      <c r="T17">
+        <v>0.571180726060833</v>
+      </c>
+      <c r="U17">
+        <v>0.048</v>
+      </c>
+      <c r="V17">
+        <v>0.25</v>
+      </c>
+      <c r="W17">
+        <v>0.036</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>8.75050875050875</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.07411163947021385</v>
+      </c>
+      <c r="C18">
+        <v>27.16609603680308</v>
+      </c>
+      <c r="D18">
+        <v>30.63809603680308</v>
+      </c>
+      <c r="E18">
+        <v>-9.032</v>
+      </c>
+      <c r="F18">
+        <v>4.368</v>
+      </c>
+      <c r="G18">
+        <v>0.896</v>
+      </c>
+      <c r="H18">
+        <v>13.9</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>2.48</v>
+      </c>
+      <c r="K18">
+        <v>0.76</v>
+      </c>
+      <c r="L18">
+        <v>1.72</v>
+      </c>
+      <c r="M18">
+        <v>0.209664</v>
+      </c>
+      <c r="N18">
+        <v>1.510336</v>
+      </c>
+      <c r="O18">
+        <v>0.377584</v>
+      </c>
+      <c r="P18">
+        <v>1.132752</v>
+      </c>
+      <c r="Q18">
+        <v>1.892752</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.0813709993693022</v>
+      </c>
+      <c r="T18">
+        <v>0.5764792485660355</v>
+      </c>
+      <c r="U18">
+        <v>0.048</v>
+      </c>
+      <c r="V18">
+        <v>0.25</v>
+      </c>
+      <c r="W18">
+        <v>0.036</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>8.203601953601954</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.07418176540909349</v>
+      </c>
+      <c r="C19">
+        <v>26.83237195406657</v>
+      </c>
+      <c r="D19">
+        <v>30.57737195406657</v>
+      </c>
+      <c r="E19">
+        <v>-8.759</v>
+      </c>
+      <c r="F19">
+        <v>4.641</v>
+      </c>
+      <c r="G19">
+        <v>0.896</v>
+      </c>
+      <c r="H19">
+        <v>13.9</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>2.48</v>
+      </c>
+      <c r="K19">
+        <v>0.76</v>
+      </c>
+      <c r="L19">
+        <v>1.72</v>
+      </c>
+      <c r="M19">
+        <v>0.2297295</v>
+      </c>
+      <c r="N19">
+        <v>1.4902705</v>
+      </c>
+      <c r="O19">
+        <v>0.372567625</v>
+      </c>
+      <c r="P19">
+        <v>1.117702875</v>
+      </c>
+      <c r="Q19">
+        <v>1.877702875</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.08177170531216084</v>
+      </c>
+      <c r="T19">
+        <v>0.5819054463123273</v>
+      </c>
+      <c r="U19">
+        <v>0.0495</v>
+      </c>
+      <c r="V19">
+        <v>0.25</v>
+      </c>
+      <c r="W19">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>7.487066310595723</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.07407189134797315</v>
+      </c>
+      <c r="C20">
+        <v>26.65462230517011</v>
+      </c>
+      <c r="D20">
+        <v>30.67262230517011</v>
+      </c>
+      <c r="E20">
+        <v>-8.486000000000001</v>
+      </c>
+      <c r="F20">
+        <v>4.914</v>
+      </c>
+      <c r="G20">
+        <v>0.896</v>
+      </c>
+      <c r="H20">
+        <v>13.9</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>2.48</v>
+      </c>
+      <c r="K20">
+        <v>0.76</v>
+      </c>
+      <c r="L20">
+        <v>1.72</v>
+      </c>
+      <c r="M20">
+        <v>0.243243</v>
+      </c>
+      <c r="N20">
+        <v>1.476757</v>
+      </c>
+      <c r="O20">
+        <v>0.36918925</v>
+      </c>
+      <c r="P20">
+        <v>1.10756775</v>
+      </c>
+      <c r="Q20">
+        <v>1.86756775</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.08218218457069895</v>
+      </c>
+      <c r="T20">
+        <v>0.5874639903451139</v>
+      </c>
+      <c r="U20">
+        <v>0.0495</v>
+      </c>
+      <c r="V20">
+        <v>0.25</v>
+      </c>
+      <c r="W20">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>7.071118182229294</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.0739620172868528</v>
+      </c>
+      <c r="C21">
+        <v>26.47746793172749</v>
+      </c>
+      <c r="D21">
+        <v>30.76846793172749</v>
+      </c>
+      <c r="E21">
+        <v>-8.213000000000001</v>
+      </c>
+      <c r="F21">
+        <v>5.187</v>
+      </c>
+      <c r="G21">
+        <v>0.896</v>
+      </c>
+      <c r="H21">
+        <v>13.9</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>2.48</v>
+      </c>
+      <c r="K21">
+        <v>0.76</v>
+      </c>
+      <c r="L21">
+        <v>1.72</v>
+      </c>
+      <c r="M21">
+        <v>0.2567565</v>
+      </c>
+      <c r="N21">
+        <v>1.4632435</v>
+      </c>
+      <c r="O21">
+        <v>0.365810875</v>
+      </c>
+      <c r="P21">
+        <v>1.097432625</v>
+      </c>
+      <c r="Q21">
+        <v>1.857432625</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.08260279911957136</v>
+      </c>
+      <c r="T21">
+        <v>0.5931597823787103</v>
+      </c>
+      <c r="U21">
+        <v>0.0495</v>
+      </c>
+      <c r="V21">
+        <v>0.25</v>
+      </c>
+      <c r="W21">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>6.698954067375119</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.07385214322573244</v>
+      </c>
+      <c r="C22">
+        <v>26.30091443157029</v>
+      </c>
+      <c r="D22">
+        <v>30.86491443157029</v>
+      </c>
+      <c r="E22">
+        <v>-7.94</v>
+      </c>
+      <c r="F22">
+        <v>5.460000000000001</v>
+      </c>
+      <c r="G22">
+        <v>0.896</v>
+      </c>
+      <c r="H22">
+        <v>13.9</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>2.48</v>
+      </c>
+      <c r="K22">
+        <v>0.76</v>
+      </c>
+      <c r="L22">
+        <v>1.72</v>
+      </c>
+      <c r="M22">
+        <v>0.2702700000000001</v>
+      </c>
+      <c r="N22">
+        <v>1.44973</v>
+      </c>
+      <c r="O22">
+        <v>0.3624325</v>
+      </c>
+      <c r="P22">
+        <v>1.0872975</v>
+      </c>
+      <c r="Q22">
+        <v>1.8472975</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.08303392903216555</v>
+      </c>
+      <c r="T22">
+        <v>0.5989979692131463</v>
+      </c>
+      <c r="U22">
+        <v>0.0495</v>
+      </c>
+      <c r="V22">
+        <v>0.25</v>
+      </c>
+      <c r="W22">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>6.364006364006363</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.07396276916461211</v>
+      </c>
+      <c r="C23">
+        <v>25.93081001634495</v>
+      </c>
+      <c r="D23">
+        <v>30.76781001634495</v>
+      </c>
+      <c r="E23">
+        <v>-7.667000000000001</v>
+      </c>
+      <c r="F23">
+        <v>5.733</v>
+      </c>
+      <c r="G23">
+        <v>0.896</v>
+      </c>
+      <c r="H23">
+        <v>13.9</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>2.48</v>
+      </c>
+      <c r="K23">
+        <v>0.76</v>
+      </c>
+      <c r="L23">
+        <v>1.72</v>
+      </c>
+      <c r="M23">
+        <v>0.2918097</v>
+      </c>
+      <c r="N23">
+        <v>1.4281903</v>
+      </c>
+      <c r="O23">
+        <v>0.357047575</v>
+      </c>
+      <c r="P23">
+        <v>1.071142725</v>
+      </c>
+      <c r="Q23">
+        <v>1.831142725</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.08347597362609127</v>
+      </c>
+      <c r="T23">
+        <v>0.6049839582459225</v>
+      </c>
+      <c r="U23">
+        <v>0.0509</v>
+      </c>
+      <c r="V23">
+        <v>0.25</v>
+      </c>
+      <c r="W23">
+        <v>0.038175</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>5.894252315807186</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.07386339510349176</v>
+      </c>
+      <c r="C24">
+        <v>25.74500985036215</v>
+      </c>
+      <c r="D24">
+        <v>30.85500985036215</v>
+      </c>
+      <c r="E24">
+        <v>-7.394</v>
+      </c>
+      <c r="F24">
+        <v>6.006</v>
+      </c>
+      <c r="G24">
+        <v>0.896</v>
+      </c>
+      <c r="H24">
+        <v>13.9</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>2.48</v>
+      </c>
+      <c r="K24">
+        <v>0.76</v>
+      </c>
+      <c r="L24">
+        <v>1.72</v>
+      </c>
+      <c r="M24">
+        <v>0.3057054</v>
+      </c>
+      <c r="N24">
+        <v>1.4142946</v>
+      </c>
+      <c r="O24">
+        <v>0.35357365</v>
+      </c>
+      <c r="P24">
+        <v>1.06072095</v>
+      </c>
+      <c r="Q24">
+        <v>1.82072095</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.0839293526967843</v>
+      </c>
+      <c r="T24">
+        <v>0.6111234341769751</v>
+      </c>
+      <c r="U24">
+        <v>0.0509</v>
+      </c>
+      <c r="V24">
+        <v>0.25</v>
+      </c>
+      <c r="W24">
+        <v>0.038175</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>5.626331755997767</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.07376402104237141</v>
+      </c>
+      <c r="C25">
+        <v>25.55970535972656</v>
+      </c>
+      <c r="D25">
+        <v>30.94270535972656</v>
+      </c>
+      <c r="E25">
+        <v>-7.121</v>
+      </c>
+      <c r="F25">
+        <v>6.279000000000001</v>
+      </c>
+      <c r="G25">
+        <v>0.896</v>
+      </c>
+      <c r="H25">
+        <v>13.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>2.48</v>
+      </c>
+      <c r="K25">
+        <v>0.76</v>
+      </c>
+      <c r="L25">
+        <v>1.72</v>
+      </c>
+      <c r="M25">
+        <v>0.3196011</v>
+      </c>
+      <c r="N25">
+        <v>1.4003989</v>
+      </c>
+      <c r="O25">
+        <v>0.350099725</v>
+      </c>
+      <c r="P25">
+        <v>1.050299175</v>
+      </c>
+      <c r="Q25">
+        <v>1.810299175</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.08439450784723559</v>
+      </c>
+      <c r="T25">
+        <v>0.6174223770153279</v>
+      </c>
+      <c r="U25">
+        <v>0.0509</v>
+      </c>
+      <c r="V25">
+        <v>0.25</v>
+      </c>
+      <c r="W25">
+        <v>0.038175</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>5.381708636171777</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.07366464698125107</v>
+      </c>
+      <c r="C26">
+        <v>25.37490078288113</v>
+      </c>
+      <c r="D26">
+        <v>31.03090078288113</v>
+      </c>
+      <c r="E26">
+        <v>-6.848000000000001</v>
+      </c>
+      <c r="F26">
+        <v>6.552</v>
+      </c>
+      <c r="G26">
+        <v>0.896</v>
+      </c>
+      <c r="H26">
+        <v>13.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>2.48</v>
+      </c>
+      <c r="K26">
+        <v>0.76</v>
+      </c>
+      <c r="L26">
+        <v>1.72</v>
+      </c>
+      <c r="M26">
+        <v>0.3334968</v>
+      </c>
+      <c r="N26">
+        <v>1.3865032</v>
+      </c>
+      <c r="O26">
+        <v>0.3466258</v>
+      </c>
+      <c r="P26">
+        <v>1.0398774</v>
+      </c>
+      <c r="Q26">
+        <v>1.7998774</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.08487190392269876</v>
+      </c>
+      <c r="T26">
+        <v>0.6238870815073214</v>
+      </c>
+      <c r="U26">
+        <v>0.0509</v>
+      </c>
+      <c r="V26">
+        <v>0.25</v>
+      </c>
+      <c r="W26">
+        <v>0.038175</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>5.157470776331287</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.07356527292013071</v>
+      </c>
+      <c r="C27">
+        <v>25.19060040672997</v>
+      </c>
+      <c r="D27">
+        <v>31.11960040672997</v>
+      </c>
+      <c r="E27">
+        <v>-6.575</v>
+      </c>
+      <c r="F27">
+        <v>6.825</v>
+      </c>
+      <c r="G27">
+        <v>0.896</v>
+      </c>
+      <c r="H27">
+        <v>13.9</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>2.48</v>
+      </c>
+      <c r="K27">
+        <v>0.76</v>
+      </c>
+      <c r="L27">
+        <v>1.72</v>
+      </c>
+      <c r="M27">
+        <v>0.3473925</v>
+      </c>
+      <c r="N27">
+        <v>1.3726075</v>
+      </c>
+      <c r="O27">
+        <v>0.343151875</v>
+      </c>
+      <c r="P27">
+        <v>1.029455625</v>
+      </c>
+      <c r="Q27">
+        <v>1.789455625</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.08536203056017427</v>
+      </c>
+      <c r="T27">
+        <v>0.6305241781191013</v>
+      </c>
+      <c r="U27">
+        <v>0.0509</v>
+      </c>
+      <c r="V27">
+        <v>0.25</v>
+      </c>
+      <c r="W27">
+        <v>0.038175</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>4.951171945278036</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.07346589885901036</v>
+      </c>
+      <c r="C28">
+        <v>25.00680856733289</v>
+      </c>
+      <c r="D28">
+        <v>31.20880856733289</v>
+      </c>
+      <c r="E28">
+        <v>-6.302</v>
+      </c>
+      <c r="F28">
+        <v>7.098000000000001</v>
+      </c>
+      <c r="G28">
+        <v>0.896</v>
+      </c>
+      <c r="H28">
+        <v>13.9</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>2.48</v>
+      </c>
+      <c r="K28">
+        <v>0.76</v>
+      </c>
+      <c r="L28">
+        <v>1.72</v>
+      </c>
+      <c r="M28">
+        <v>0.3612882000000001</v>
+      </c>
+      <c r="N28">
+        <v>1.3587118</v>
+      </c>
+      <c r="O28">
+        <v>0.33967795</v>
+      </c>
+      <c r="P28">
+        <v>1.01903385</v>
+      </c>
+      <c r="Q28">
+        <v>1.77903385</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.08586540386352751</v>
+      </c>
+      <c r="T28">
+        <v>0.637340655720389</v>
+      </c>
+      <c r="U28">
+        <v>0.0509</v>
+      </c>
+      <c r="V28">
+        <v>0.25</v>
+      </c>
+      <c r="W28">
+        <v>0.038175</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>4.760742255075034</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.07336652479789002</v>
+      </c>
+      <c r="C29">
+        <v>24.82352965061206</v>
+      </c>
+      <c r="D29">
+        <v>31.29852965061206</v>
+      </c>
+      <c r="E29">
+        <v>-6.029</v>
+      </c>
+      <c r="F29">
+        <v>7.371</v>
+      </c>
+      <c r="G29">
+        <v>0.896</v>
+      </c>
+      <c r="H29">
+        <v>13.9</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>2.48</v>
+      </c>
+      <c r="K29">
+        <v>0.76</v>
+      </c>
+      <c r="L29">
+        <v>1.72</v>
+      </c>
+      <c r="M29">
+        <v>0.3751839</v>
+      </c>
+      <c r="N29">
+        <v>1.3448161</v>
+      </c>
+      <c r="O29">
+        <v>0.336204025</v>
+      </c>
+      <c r="P29">
+        <v>1.008612075</v>
+      </c>
+      <c r="Q29">
+        <v>1.768612075</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.08638256821628769</v>
+      </c>
+      <c r="T29">
+        <v>0.6443438861326708</v>
+      </c>
+      <c r="U29">
+        <v>0.0509</v>
+      </c>
+      <c r="V29">
+        <v>0.25</v>
+      </c>
+      <c r="W29">
+        <v>0.038175</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>4.584418467850034</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.07381315073676967</v>
+      </c>
+      <c r="C30">
+        <v>24.15128722607708</v>
+      </c>
+      <c r="D30">
+        <v>30.89928722607708</v>
+      </c>
+      <c r="E30">
+        <v>-5.755999999999999</v>
+      </c>
+      <c r="F30">
+        <v>7.644000000000001</v>
+      </c>
+      <c r="G30">
+        <v>0.896</v>
+      </c>
+      <c r="H30">
+        <v>13.9</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>2.48</v>
+      </c>
+      <c r="K30">
+        <v>0.76</v>
+      </c>
+      <c r="L30">
+        <v>1.72</v>
+      </c>
+      <c r="M30">
+        <v>0.408954</v>
+      </c>
+      <c r="N30">
+        <v>1.311046</v>
+      </c>
+      <c r="O30">
+        <v>0.3277615</v>
+      </c>
+      <c r="P30">
+        <v>0.9832844999999999</v>
+      </c>
+      <c r="Q30">
+        <v>1.7432845</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.08691409824551342</v>
+      </c>
+      <c r="T30">
+        <v>0.6515416507230715</v>
+      </c>
+      <c r="U30">
+        <v>0.0535</v>
+      </c>
+      <c r="V30">
+        <v>0.25</v>
+      </c>
+      <c r="W30">
+        <v>0.040125</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>4.205852002914753</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.0737332766756493</v>
+      </c>
+      <c r="C31">
+        <v>23.94893767147866</v>
+      </c>
+      <c r="D31">
+        <v>30.96993767147866</v>
+      </c>
+      <c r="E31">
+        <v>-5.483000000000001</v>
+      </c>
+      <c r="F31">
+        <v>7.917</v>
+      </c>
+      <c r="G31">
+        <v>0.896</v>
+      </c>
+      <c r="H31">
+        <v>13.9</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>2.48</v>
+      </c>
+      <c r="K31">
+        <v>0.76</v>
+      </c>
+      <c r="L31">
+        <v>1.72</v>
+      </c>
+      <c r="M31">
+        <v>0.4235595</v>
+      </c>
+      <c r="N31">
+        <v>1.2964405</v>
+      </c>
+      <c r="O31">
+        <v>0.324110125</v>
+      </c>
+      <c r="P31">
+        <v>0.9723303750000001</v>
+      </c>
+      <c r="Q31">
+        <v>1.732330375</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.08746060095161874</v>
+      </c>
+      <c r="T31">
+        <v>0.658942169245596</v>
+      </c>
+      <c r="U31">
+        <v>0.0535</v>
+      </c>
+      <c r="V31">
+        <v>0.25</v>
+      </c>
+      <c r="W31">
+        <v>0.040125</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>4.0608226235039</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.07426090261452896</v>
+      </c>
+      <c r="C32">
+        <v>23.21513320131091</v>
+      </c>
+      <c r="D32">
+        <v>30.5091332013109</v>
+      </c>
+      <c r="E32">
+        <v>-5.210000000000001</v>
+      </c>
+      <c r="F32">
+        <v>8.19</v>
+      </c>
+      <c r="G32">
+        <v>0.896</v>
+      </c>
+      <c r="H32">
+        <v>13.9</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>2.48</v>
+      </c>
+      <c r="K32">
+        <v>0.76</v>
+      </c>
+      <c r="L32">
+        <v>1.72</v>
+      </c>
+      <c r="M32">
+        <v>0.460278</v>
+      </c>
+      <c r="N32">
+        <v>1.259722</v>
+      </c>
+      <c r="O32">
+        <v>0.3149305</v>
+      </c>
+      <c r="P32">
+        <v>0.9447915</v>
+      </c>
+      <c r="Q32">
+        <v>1.7047915</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.08802271802075566</v>
+      </c>
+      <c r="T32">
+        <v>0.6665541311544786</v>
+      </c>
+      <c r="U32">
+        <v>0.0562</v>
+      </c>
+      <c r="V32">
+        <v>0.25</v>
+      </c>
+      <c r="W32">
+        <v>0.04215</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>3.7368720642742</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.07420127855340861</v>
+      </c>
+      <c r="C33">
+        <v>22.99351774156075</v>
+      </c>
+      <c r="D33">
+        <v>30.56051774156075</v>
+      </c>
+      <c r="E33">
+        <v>-4.936999999999999</v>
+      </c>
+      <c r="F33">
+        <v>8.463000000000001</v>
+      </c>
+      <c r="G33">
+        <v>0.896</v>
+      </c>
+      <c r="H33">
+        <v>13.9</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>2.48</v>
+      </c>
+      <c r="K33">
+        <v>0.76</v>
+      </c>
+      <c r="L33">
+        <v>1.72</v>
+      </c>
+      <c r="M33">
+        <v>0.4756206000000001</v>
+      </c>
+      <c r="N33">
+        <v>1.2443794</v>
+      </c>
+      <c r="O33">
+        <v>0.31109485</v>
+      </c>
+      <c r="P33">
+        <v>0.93328455</v>
+      </c>
+      <c r="Q33">
+        <v>1.69328455</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.08860112833827335</v>
+      </c>
+      <c r="T33">
+        <v>0.6743867296404301</v>
+      </c>
+      <c r="U33">
+        <v>0.0562</v>
+      </c>
+      <c r="V33">
+        <v>0.25</v>
+      </c>
+      <c r="W33">
+        <v>0.04215</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>3.616327804136322</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.07414165449228827</v>
+      </c>
+      <c r="C34">
+        <v>22.77207566107156</v>
+      </c>
+      <c r="D34">
+        <v>30.61207566107156</v>
+      </c>
+      <c r="E34">
+        <v>-4.664</v>
+      </c>
+      <c r="F34">
+        <v>8.736000000000001</v>
+      </c>
+      <c r="G34">
+        <v>0.896</v>
+      </c>
+      <c r="H34">
+        <v>13.9</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>2.48</v>
+      </c>
+      <c r="K34">
+        <v>0.76</v>
+      </c>
+      <c r="L34">
+        <v>1.72</v>
+      </c>
+      <c r="M34">
+        <v>0.4909632</v>
+      </c>
+      <c r="N34">
+        <v>1.2290368</v>
+      </c>
+      <c r="O34">
+        <v>0.3072592</v>
+      </c>
+      <c r="P34">
+        <v>0.9217775999999999</v>
+      </c>
+      <c r="Q34">
+        <v>1.6817776</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.08919655072395333</v>
+      </c>
+      <c r="T34">
+        <v>0.6824496986700862</v>
+      </c>
+      <c r="U34">
+        <v>0.0562</v>
+      </c>
+      <c r="V34">
+        <v>0.25</v>
+      </c>
+      <c r="W34">
+        <v>0.04215</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>3.503317560257062</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.07524528043116792</v>
+      </c>
+      <c r="C35">
+        <v>21.57208922159797</v>
+      </c>
+      <c r="D35">
+        <v>29.68508922159797</v>
+      </c>
+      <c r="E35">
+        <v>-4.391</v>
+      </c>
+      <c r="F35">
+        <v>9.009</v>
+      </c>
+      <c r="G35">
+        <v>0.896</v>
+      </c>
+      <c r="H35">
+        <v>13.9</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>2.48</v>
+      </c>
+      <c r="K35">
+        <v>0.76</v>
+      </c>
+      <c r="L35">
+        <v>1.72</v>
+      </c>
+      <c r="M35">
+        <v>0.5486481000000001</v>
+      </c>
+      <c r="N35">
+        <v>1.1713519</v>
+      </c>
+      <c r="O35">
+        <v>0.292837975</v>
+      </c>
+      <c r="P35">
+        <v>0.8785139249999999</v>
+      </c>
+      <c r="Q35">
+        <v>1.638513925</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.08980974691219093</v>
+      </c>
+      <c r="T35">
+        <v>0.6907533533424186</v>
+      </c>
+      <c r="U35">
+        <v>0.0609</v>
+      </c>
+      <c r="V35">
+        <v>0.25</v>
+      </c>
+      <c r="W35">
+        <v>0.045675</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>3.134978504436632</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.07522090637004757</v>
+      </c>
+      <c r="C36">
+        <v>21.31895545369277</v>
+      </c>
+      <c r="D36">
+        <v>29.70495545369277</v>
+      </c>
+      <c r="E36">
+        <v>-4.118</v>
+      </c>
+      <c r="F36">
+        <v>9.282</v>
+      </c>
+      <c r="G36">
+        <v>0.896</v>
+      </c>
+      <c r="H36">
+        <v>13.9</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>2.48</v>
+      </c>
+      <c r="K36">
+        <v>0.76</v>
+      </c>
+      <c r="L36">
+        <v>1.72</v>
+      </c>
+      <c r="M36">
+        <v>0.5652738</v>
+      </c>
+      <c r="N36">
+        <v>1.1547262</v>
+      </c>
+      <c r="O36">
+        <v>0.28868155</v>
+      </c>
+      <c r="P36">
+        <v>0.8660446499999999</v>
+      </c>
+      <c r="Q36">
+        <v>1.62604465</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.09044152480310239</v>
+      </c>
+      <c r="T36">
+        <v>0.6993086339139125</v>
+      </c>
+      <c r="U36">
+        <v>0.0609</v>
+      </c>
+      <c r="V36">
+        <v>0.25</v>
+      </c>
+      <c r="W36">
+        <v>0.045675</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>3.042773254306143</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.07763778230892722</v>
+      </c>
+      <c r="C37">
+        <v>19.19741550539042</v>
+      </c>
+      <c r="D37">
+        <v>27.85641550539042</v>
+      </c>
+      <c r="E37">
+        <v>-3.844999999999999</v>
+      </c>
+      <c r="F37">
+        <v>9.555000000000001</v>
+      </c>
+      <c r="G37">
+        <v>0.896</v>
+      </c>
+      <c r="H37">
+        <v>13.9</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>2.48</v>
+      </c>
+      <c r="K37">
+        <v>0.76</v>
+      </c>
+      <c r="L37">
+        <v>1.72</v>
+      </c>
+      <c r="M37">
+        <v>0.6707610000000001</v>
+      </c>
+      <c r="N37">
+        <v>1.049239</v>
+      </c>
+      <c r="O37">
+        <v>0.26230975</v>
+      </c>
+      <c r="P37">
+        <v>0.78692925</v>
+      </c>
+      <c r="Q37">
+        <v>1.54692925</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.09109274201373418</v>
+      </c>
+      <c r="T37">
+        <v>0.7081271538876062</v>
+      </c>
+      <c r="U37">
+        <v>0.0702</v>
+      </c>
+      <c r="V37">
+        <v>0.25</v>
+      </c>
+      <c r="W37">
+        <v>0.05265</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>2.564251648500733</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.07895215824780688</v>
+      </c>
+      <c r="C38">
+        <v>18.0125391858723</v>
+      </c>
+      <c r="D38">
+        <v>26.9445391858723</v>
+      </c>
+      <c r="E38">
+        <v>-3.572000000000001</v>
+      </c>
+      <c r="F38">
+        <v>9.827999999999999</v>
+      </c>
+      <c r="G38">
+        <v>0.896</v>
+      </c>
+      <c r="H38">
+        <v>13.9</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>2.48</v>
+      </c>
+      <c r="K38">
+        <v>0.76</v>
+      </c>
+      <c r="L38">
+        <v>1.72</v>
+      </c>
+      <c r="M38">
+        <v>0.7361171999999999</v>
+      </c>
+      <c r="N38">
+        <v>0.9838828000000001</v>
+      </c>
+      <c r="O38">
+        <v>0.2459707</v>
+      </c>
+      <c r="P38">
+        <v>0.7379121000000001</v>
+      </c>
+      <c r="Q38">
+        <v>1.4979121</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.09176430976219824</v>
+      </c>
+      <c r="T38">
+        <v>0.7172212526104778</v>
+      </c>
+      <c r="U38">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V38">
+        <v>0.25</v>
+      </c>
+      <c r="W38">
+        <v>0.056175</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>2.336584446063752</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.07903278418668652</v>
+      </c>
+      <c r="C39">
+        <v>17.68554270480701</v>
+      </c>
+      <c r="D39">
+        <v>26.89054270480701</v>
+      </c>
+      <c r="E39">
+        <v>-3.298999999999999</v>
+      </c>
+      <c r="F39">
+        <v>10.101</v>
+      </c>
+      <c r="G39">
+        <v>0.896</v>
+      </c>
+      <c r="H39">
+        <v>13.9</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>2.48</v>
+      </c>
+      <c r="K39">
+        <v>0.76</v>
+      </c>
+      <c r="L39">
+        <v>1.72</v>
+      </c>
+      <c r="M39">
+        <v>0.7565649</v>
+      </c>
+      <c r="N39">
+        <v>0.9634351</v>
+      </c>
+      <c r="O39">
+        <v>0.240858775</v>
+      </c>
+      <c r="P39">
+        <v>0.722576325</v>
+      </c>
+      <c r="Q39">
+        <v>1.482576325</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.09245719712172465</v>
+      </c>
+      <c r="T39">
+        <v>0.7266040528801073</v>
+      </c>
+      <c r="U39">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V39">
+        <v>0.25</v>
+      </c>
+      <c r="W39">
+        <v>0.056175</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>2.273433515089056</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.07911341012556616</v>
+      </c>
+      <c r="C40">
+        <v>17.35876220730493</v>
+      </c>
+      <c r="D40">
+        <v>26.83676220730493</v>
+      </c>
+      <c r="E40">
+        <v>-3.026</v>
+      </c>
+      <c r="F40">
+        <v>10.374</v>
+      </c>
+      <c r="G40">
+        <v>0.896</v>
+      </c>
+      <c r="H40">
+        <v>13.9</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>2.48</v>
+      </c>
+      <c r="K40">
+        <v>0.76</v>
+      </c>
+      <c r="L40">
+        <v>1.72</v>
+      </c>
+      <c r="M40">
+        <v>0.7770125999999999</v>
+      </c>
+      <c r="N40">
+        <v>0.9429874</v>
+      </c>
+      <c r="O40">
+        <v>0.23574685</v>
+      </c>
+      <c r="P40">
+        <v>0.7072405500000001</v>
+      </c>
+      <c r="Q40">
+        <v>1.46724055</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.09317243568639705</v>
+      </c>
+      <c r="T40">
+        <v>0.7362895241261764</v>
+      </c>
+      <c r="U40">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V40">
+        <v>0.25</v>
+      </c>
+      <c r="W40">
+        <v>0.056175</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>2.213606317323555</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.07919403606444583</v>
+      </c>
+      <c r="C41">
+        <v>17.03219640006542</v>
+      </c>
+      <c r="D41">
+        <v>26.78319640006541</v>
+      </c>
+      <c r="E41">
+        <v>-2.753</v>
+      </c>
+      <c r="F41">
+        <v>10.647</v>
+      </c>
+      <c r="G41">
+        <v>0.896</v>
+      </c>
+      <c r="H41">
+        <v>13.9</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>2.48</v>
+      </c>
+      <c r="K41">
+        <v>0.76</v>
+      </c>
+      <c r="L41">
+        <v>1.72</v>
+      </c>
+      <c r="M41">
+        <v>0.7974603</v>
+      </c>
+      <c r="N41">
+        <v>0.9225397</v>
+      </c>
+      <c r="O41">
+        <v>0.230634925</v>
+      </c>
+      <c r="P41">
+        <v>0.691904775</v>
+      </c>
+      <c r="Q41">
+        <v>1.451904775</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.09391112469581284</v>
+      </c>
+      <c r="T41">
+        <v>0.746292551806543</v>
+      </c>
+      <c r="U41">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V41">
+        <v>0.25</v>
+      </c>
+      <c r="W41">
+        <v>0.056175</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>2.156847180981925</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.07927466200332547</v>
+      </c>
+      <c r="C42">
+        <v>16.70584400009291</v>
+      </c>
+      <c r="D42">
+        <v>26.72984400009291</v>
+      </c>
+      <c r="E42">
+        <v>-2.479999999999999</v>
+      </c>
+      <c r="F42">
+        <v>10.92</v>
+      </c>
+      <c r="G42">
+        <v>0.896</v>
+      </c>
+      <c r="H42">
+        <v>13.9</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>2.48</v>
+      </c>
+      <c r="K42">
+        <v>0.76</v>
+      </c>
+      <c r="L42">
+        <v>1.72</v>
+      </c>
+      <c r="M42">
+        <v>0.8179080000000001</v>
+      </c>
+      <c r="N42">
+        <v>0.9020919999999999</v>
+      </c>
+      <c r="O42">
+        <v>0.225523</v>
+      </c>
+      <c r="P42">
+        <v>0.676569</v>
+      </c>
+      <c r="Q42">
+        <v>1.436569</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.09467443667220914</v>
+      </c>
+      <c r="T42">
+        <v>0.7566290137429217</v>
+      </c>
+      <c r="U42">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V42">
+        <v>0.25</v>
+      </c>
+      <c r="W42">
+        <v>0.056175</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>2.102926001457377</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.07935528794220514</v>
+      </c>
+      <c r="C43">
+        <v>16.37970373459447</v>
+      </c>
+      <c r="D43">
+        <v>26.67670373459447</v>
+      </c>
+      <c r="E43">
+        <v>-2.206999999999999</v>
+      </c>
+      <c r="F43">
+        <v>11.193</v>
+      </c>
+      <c r="G43">
+        <v>0.896</v>
+      </c>
+      <c r="H43">
+        <v>13.9</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>2.48</v>
+      </c>
+      <c r="K43">
+        <v>0.76</v>
+      </c>
+      <c r="L43">
+        <v>1.72</v>
+      </c>
+      <c r="M43">
+        <v>0.8383557</v>
+      </c>
+      <c r="N43">
+        <v>0.8816442999999999</v>
+      </c>
+      <c r="O43">
+        <v>0.220411075</v>
+      </c>
+      <c r="P43">
+        <v>0.6612332249999999</v>
+      </c>
+      <c r="Q43">
+        <v>1.421233225</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.09546362363085617</v>
+      </c>
+      <c r="T43">
+        <v>0.7673158642195167</v>
+      </c>
+      <c r="U43">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V43">
+        <v>0.25</v>
+      </c>
+      <c r="W43">
+        <v>0.056175</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>2.051635123373051</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.07943591388108479</v>
+      </c>
+      <c r="C44">
+        <v>16.05377434087861</v>
+      </c>
+      <c r="D44">
+        <v>26.62377434087861</v>
+      </c>
+      <c r="E44">
+        <v>-1.934000000000001</v>
+      </c>
+      <c r="F44">
+        <v>11.466</v>
+      </c>
+      <c r="G44">
+        <v>0.896</v>
+      </c>
+      <c r="H44">
+        <v>13.9</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>2.48</v>
+      </c>
+      <c r="K44">
+        <v>0.76</v>
+      </c>
+      <c r="L44">
+        <v>1.72</v>
+      </c>
+      <c r="M44">
+        <v>0.8588033999999999</v>
+      </c>
+      <c r="N44">
+        <v>0.8611966000000001</v>
+      </c>
+      <c r="O44">
+        <v>0.21529915</v>
+      </c>
+      <c r="P44">
+        <v>0.6458974500000001</v>
+      </c>
+      <c r="Q44">
+        <v>1.40589745</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.0962800239329048</v>
+      </c>
+      <c r="T44">
+        <v>0.7783712267815114</v>
+      </c>
+      <c r="U44">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V44">
+        <v>0.25</v>
+      </c>
+      <c r="W44">
+        <v>0.056175</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>2.002786668054645</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.08477328981996443</v>
+      </c>
+      <c r="C45">
+        <v>12.68982537625921</v>
+      </c>
+      <c r="D45">
+        <v>23.53282537625921</v>
+      </c>
+      <c r="E45">
+        <v>-1.661</v>
+      </c>
+      <c r="F45">
+        <v>11.739</v>
+      </c>
+      <c r="G45">
+        <v>0.896</v>
+      </c>
+      <c r="H45">
+        <v>13.9</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>2.48</v>
+      </c>
+      <c r="K45">
+        <v>0.76</v>
+      </c>
+      <c r="L45">
+        <v>1.72</v>
+      </c>
+      <c r="M45">
+        <v>1.0705968</v>
+      </c>
+      <c r="N45">
+        <v>0.6494031999999998</v>
+      </c>
+      <c r="O45">
+        <v>0.1623508</v>
+      </c>
+      <c r="P45">
+        <v>0.4870523999999999</v>
+      </c>
+      <c r="Q45">
+        <v>1.2470524</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.09712506985958672</v>
+      </c>
+      <c r="T45">
+        <v>0.7898144968018216</v>
+      </c>
+      <c r="U45">
+        <v>0.0912</v>
+      </c>
+      <c r="V45">
+        <v>0.25</v>
+      </c>
+      <c r="W45">
+        <v>0.0684</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>1.606580553948975</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.08497616575884409</v>
+      </c>
+      <c r="C46">
+        <v>12.31343342146519</v>
+      </c>
+      <c r="D46">
+        <v>23.42943342146519</v>
+      </c>
+      <c r="E46">
+        <v>-1.388</v>
+      </c>
+      <c r="F46">
+        <v>12.012</v>
+      </c>
+      <c r="G46">
+        <v>0.896</v>
+      </c>
+      <c r="H46">
+        <v>13.9</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>2.48</v>
+      </c>
+      <c r="K46">
+        <v>0.76</v>
+      </c>
+      <c r="L46">
+        <v>1.72</v>
+      </c>
+      <c r="M46">
+        <v>1.0954944</v>
+      </c>
+      <c r="N46">
+        <v>0.6245056</v>
+      </c>
+      <c r="O46">
+        <v>0.1561264</v>
+      </c>
+      <c r="P46">
+        <v>0.4683792</v>
+      </c>
+      <c r="Q46">
+        <v>1.2283792</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.09800029599793586</v>
+      </c>
+      <c r="T46">
+        <v>0.8016664550371432</v>
+      </c>
+      <c r="U46">
+        <v>0.0912</v>
+      </c>
+      <c r="V46">
+        <v>0.25</v>
+      </c>
+      <c r="W46">
+        <v>0.0684</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>1.570067359541044</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.08517904169772374</v>
+      </c>
+      <c r="C47">
+        <v>11.93794600195839</v>
+      </c>
+      <c r="D47">
+        <v>23.32694600195839</v>
+      </c>
+      <c r="E47">
+        <v>-1.115</v>
+      </c>
+      <c r="F47">
+        <v>12.285</v>
+      </c>
+      <c r="G47">
+        <v>0.896</v>
+      </c>
+      <c r="H47">
+        <v>13.9</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>2.48</v>
+      </c>
+      <c r="K47">
+        <v>0.76</v>
+      </c>
+      <c r="L47">
+        <v>1.72</v>
+      </c>
+      <c r="M47">
+        <v>1.120392</v>
+      </c>
+      <c r="N47">
+        <v>0.5996079999999999</v>
+      </c>
+      <c r="O47">
+        <v>0.149902</v>
+      </c>
+      <c r="P47">
+        <v>0.4497059999999999</v>
+      </c>
+      <c r="Q47">
+        <v>1.209706</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.09890734854131587</v>
+      </c>
+      <c r="T47">
+        <v>0.8139493935719307</v>
+      </c>
+      <c r="U47">
+        <v>0.0912</v>
+      </c>
+      <c r="V47">
+        <v>0.25</v>
+      </c>
+      <c r="W47">
+        <v>0.0684</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>1.535176973773465</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.08538191763660338</v>
+      </c>
+      <c r="C48">
+        <v>11.56335129930442</v>
+      </c>
+      <c r="D48">
+        <v>23.22535129930442</v>
+      </c>
+      <c r="E48">
+        <v>-0.8419999999999987</v>
+      </c>
+      <c r="F48">
+        <v>12.558</v>
+      </c>
+      <c r="G48">
+        <v>0.896</v>
+      </c>
+      <c r="H48">
+        <v>13.9</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>2.48</v>
+      </c>
+      <c r="K48">
+        <v>0.76</v>
+      </c>
+      <c r="L48">
+        <v>1.72</v>
+      </c>
+      <c r="M48">
+        <v>1.1452896</v>
+      </c>
+      <c r="N48">
+        <v>0.5747103999999998</v>
+      </c>
+      <c r="O48">
+        <v>0.1436776</v>
+      </c>
+      <c r="P48">
+        <v>0.4310327999999999</v>
+      </c>
+      <c r="Q48">
+        <v>1.1910328</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.0998479956233396</v>
+      </c>
+      <c r="T48">
+        <v>0.8266872557561551</v>
+      </c>
+      <c r="U48">
+        <v>0.0912</v>
+      </c>
+      <c r="V48">
+        <v>0.25</v>
+      </c>
+      <c r="W48">
+        <v>0.0684</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>1.501803561300129</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1119181205973776</v>
+      </c>
+      <c r="C49">
+        <v>2.861351334886196</v>
+      </c>
+      <c r="D49">
+        <v>14.7963513348862</v>
+      </c>
+      <c r="E49">
+        <v>-0.5689999999999991</v>
+      </c>
+      <c r="F49">
+        <v>12.831</v>
+      </c>
+      <c r="G49">
+        <v>0.896</v>
+      </c>
+      <c r="H49">
+        <v>13.9</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>2.48</v>
+      </c>
+      <c r="K49">
+        <v>0.76</v>
+      </c>
+      <c r="L49">
+        <v>1.72</v>
+      </c>
+      <c r="M49">
+        <v>2.0093346</v>
+      </c>
+      <c r="N49">
+        <v>-0.2893346000000003</v>
+      </c>
+      <c r="O49">
+        <v>-0.07233365000000008</v>
+      </c>
+      <c r="P49">
+        <v>-0.2170009500000002</v>
+      </c>
+      <c r="Q49">
+        <v>0.5429990499999997</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1020132761288554</v>
+      </c>
+      <c r="T49">
+        <v>0.8560086082554462</v>
+      </c>
+      <c r="U49">
+        <v>0.1566</v>
+      </c>
+      <c r="V49">
+        <v>0.2140011922354793</v>
+      </c>
+      <c r="W49">
+        <v>0.123087413295924</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.8560047689419172</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1130961205973776</v>
+      </c>
+      <c r="C50">
+        <v>2.35374821251118</v>
+      </c>
+      <c r="D50">
+        <v>14.56174821251118</v>
+      </c>
+      <c r="E50">
+        <v>-0.2960000000000012</v>
+      </c>
+      <c r="F50">
+        <v>13.104</v>
+      </c>
+      <c r="G50">
+        <v>0.896</v>
+      </c>
+      <c r="H50">
+        <v>13.9</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>2.48</v>
+      </c>
+      <c r="K50">
+        <v>0.76</v>
+      </c>
+      <c r="L50">
+        <v>1.72</v>
+      </c>
+      <c r="M50">
+        <v>2.0520864</v>
+      </c>
+      <c r="N50">
+        <v>-0.3320864000000003</v>
+      </c>
+      <c r="O50">
+        <v>-0.08302160000000008</v>
+      </c>
+      <c r="P50">
+        <v>-0.2490648000000003</v>
+      </c>
+      <c r="Q50">
+        <v>0.5109351999999998</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1032289160544103</v>
+      </c>
+      <c r="T50">
+        <v>0.8724703122603586</v>
+      </c>
+      <c r="U50">
+        <v>0.1566</v>
+      </c>
+      <c r="V50">
+        <v>0.2095428340639068</v>
+      </c>
+      <c r="W50">
+        <v>0.1237855921855922</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.8381713362556273</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1142741205973776</v>
+      </c>
+      <c r="C51">
+        <v>1.853468460742407</v>
+      </c>
+      <c r="D51">
+        <v>14.33446846074241</v>
+      </c>
+      <c r="E51">
+        <v>-0.02299999999999969</v>
+      </c>
+      <c r="F51">
+        <v>13.377</v>
+      </c>
+      <c r="G51">
+        <v>0.896</v>
+      </c>
+      <c r="H51">
+        <v>13.9</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>2.48</v>
+      </c>
+      <c r="K51">
+        <v>0.76</v>
+      </c>
+      <c r="L51">
+        <v>1.72</v>
+      </c>
+      <c r="M51">
+        <v>2.0948382</v>
+      </c>
+      <c r="N51">
+        <v>-0.3748382000000003</v>
+      </c>
+      <c r="O51">
+        <v>-0.09370955000000009</v>
+      </c>
+      <c r="P51">
+        <v>-0.2811286500000003</v>
+      </c>
+      <c r="Q51">
+        <v>0.4788713499999998</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1044922281339085</v>
+      </c>
+      <c r="T51">
+        <v>0.8895775732850716</v>
+      </c>
+      <c r="U51">
+        <v>0.1566</v>
+      </c>
+      <c r="V51">
+        <v>0.2052664496952557</v>
+      </c>
+      <c r="W51">
+        <v>0.124455273977723</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.8210657987810227</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1154521205973776</v>
+      </c>
+      <c r="C52">
+        <v>1.36017443997487</v>
+      </c>
+      <c r="D52">
+        <v>14.11417443997487</v>
+      </c>
+      <c r="E52">
+        <v>0.25</v>
+      </c>
+      <c r="F52">
+        <v>13.65</v>
+      </c>
+      <c r="G52">
+        <v>0.896</v>
+      </c>
+      <c r="H52">
+        <v>13.9</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>2.48</v>
+      </c>
+      <c r="K52">
+        <v>0.76</v>
+      </c>
+      <c r="L52">
+        <v>1.72</v>
+      </c>
+      <c r="M52">
+        <v>2.13759</v>
+      </c>
+      <c r="N52">
+        <v>-0.4175900000000003</v>
+      </c>
+      <c r="O52">
+        <v>-0.1043975000000001</v>
+      </c>
+      <c r="P52">
+        <v>-0.3131925000000003</v>
+      </c>
+      <c r="Q52">
+        <v>0.4468074999999997</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1058060726965867</v>
+      </c>
+      <c r="T52">
+        <v>0.907369124750773</v>
+      </c>
+      <c r="U52">
+        <v>0.1566</v>
+      </c>
+      <c r="V52">
+        <v>0.2011611207013506</v>
+      </c>
+      <c r="W52">
+        <v>0.1250981684981685</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.8046444828054022</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1441887676223391</v>
+      </c>
+      <c r="C53">
+        <v>-2.761376578134943</v>
+      </c>
+      <c r="D53">
+        <v>10.26562342186506</v>
+      </c>
+      <c r="E53">
+        <v>0.5229999999999997</v>
+      </c>
+      <c r="F53">
+        <v>13.923</v>
+      </c>
+      <c r="G53">
+        <v>0.896</v>
+      </c>
+      <c r="H53">
+        <v>13.9</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>2.48</v>
+      </c>
+      <c r="K53">
+        <v>0.76</v>
+      </c>
+      <c r="L53">
+        <v>1.72</v>
+      </c>
+      <c r="M53">
+        <v>2.9071224</v>
+      </c>
+      <c r="N53">
+        <v>-1.1871224</v>
+      </c>
+      <c r="O53">
+        <v>-0.2967806</v>
+      </c>
+      <c r="P53">
+        <v>-0.8903418000000001</v>
+      </c>
+      <c r="Q53">
+        <v>-0.1303418000000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1090850681086834</v>
+      </c>
+      <c r="T53">
+        <v>0.9517719538884901</v>
+      </c>
+      <c r="U53">
+        <v>0.2088</v>
+      </c>
+      <c r="V53">
+        <v>0.1479125887509931</v>
+      </c>
+      <c r="W53">
+        <v>0.1779158514687927</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.5916503550039722</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1458887676223391</v>
+      </c>
+      <c r="C54">
+        <v>-3.197340072856592</v>
+      </c>
+      <c r="D54">
+        <v>10.10265992714341</v>
+      </c>
+      <c r="E54">
+        <v>0.7960000000000012</v>
+      </c>
+      <c r="F54">
+        <v>14.196</v>
+      </c>
+      <c r="G54">
+        <v>0.896</v>
+      </c>
+      <c r="H54">
+        <v>13.9</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>2.48</v>
+      </c>
+      <c r="K54">
+        <v>0.76</v>
+      </c>
+      <c r="L54">
+        <v>1.72</v>
+      </c>
+      <c r="M54">
+        <v>2.9641248</v>
+      </c>
+      <c r="N54">
+        <v>-1.2441248</v>
+      </c>
+      <c r="O54">
+        <v>-0.3110312000000001</v>
+      </c>
+      <c r="P54">
+        <v>-0.9330936000000003</v>
+      </c>
+      <c r="Q54">
+        <v>-0.1730936000000003</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1105493403609476</v>
+      </c>
+      <c r="T54">
+        <v>0.9716005362611672</v>
+      </c>
+      <c r="U54">
+        <v>0.2088</v>
+      </c>
+      <c r="V54">
+        <v>0.145068115890397</v>
+      </c>
+      <c r="W54">
+        <v>0.1785097774020851</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.5802724635615881</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1475887676223391</v>
+      </c>
+      <c r="C55">
+        <v>-3.628210432559216</v>
+      </c>
+      <c r="D55">
+        <v>9.944789567440784</v>
+      </c>
+      <c r="E55">
+        <v>1.069000000000001</v>
+      </c>
+      <c r="F55">
+        <v>14.469</v>
+      </c>
+      <c r="G55">
+        <v>0.896</v>
+      </c>
+      <c r="H55">
+        <v>13.9</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>2.48</v>
+      </c>
+      <c r="K55">
+        <v>0.76</v>
+      </c>
+      <c r="L55">
+        <v>1.72</v>
+      </c>
+      <c r="M55">
+        <v>3.0211272</v>
+      </c>
+      <c r="N55">
+        <v>-1.3011272</v>
+      </c>
+      <c r="O55">
+        <v>-0.3252818000000001</v>
+      </c>
+      <c r="P55">
+        <v>-0.9758454000000003</v>
+      </c>
+      <c r="Q55">
+        <v>-0.2158454000000003</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.112075922070755</v>
+      </c>
+      <c r="T55">
+        <v>0.992272888096511</v>
+      </c>
+      <c r="U55">
+        <v>0.2088</v>
+      </c>
+      <c r="V55">
+        <v>0.1423309816283141</v>
+      </c>
+      <c r="W55">
+        <v>0.179081291036008</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.5693239265132564</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1492887676223391</v>
+      </c>
+      <c r="C56">
+        <v>-4.054222748910107</v>
+      </c>
+      <c r="D56">
+        <v>9.791777251089893</v>
+      </c>
+      <c r="E56">
+        <v>1.342000000000001</v>
+      </c>
+      <c r="F56">
+        <v>14.742</v>
+      </c>
+      <c r="G56">
+        <v>0.896</v>
+      </c>
+      <c r="H56">
+        <v>13.9</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>2.48</v>
+      </c>
+      <c r="K56">
+        <v>0.76</v>
+      </c>
+      <c r="L56">
+        <v>1.72</v>
+      </c>
+      <c r="M56">
+        <v>3.0781296</v>
+      </c>
+      <c r="N56">
+        <v>-1.3581296</v>
+      </c>
+      <c r="O56">
+        <v>-0.3395324000000001</v>
+      </c>
+      <c r="P56">
+        <v>-1.0185972</v>
+      </c>
+      <c r="Q56">
+        <v>-0.2585972000000003</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1136688768983802</v>
+      </c>
+      <c r="T56">
+        <v>1.01384403783774</v>
+      </c>
+      <c r="U56">
+        <v>0.2088</v>
+      </c>
+      <c r="V56">
+        <v>0.1396952227092712</v>
+      </c>
+      <c r="W56">
+        <v>0.1796316374983042</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.5587808908370848</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1509887676223391</v>
+      </c>
+      <c r="C57">
+        <v>-4.475597864170203</v>
+      </c>
+      <c r="D57">
+        <v>9.643402135829799</v>
+      </c>
+      <c r="E57">
+        <v>1.615000000000002</v>
+      </c>
+      <c r="F57">
+        <v>15.015</v>
+      </c>
+      <c r="G57">
+        <v>0.896</v>
+      </c>
+      <c r="H57">
+        <v>13.9</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>2.48</v>
+      </c>
+      <c r="K57">
+        <v>0.76</v>
+      </c>
+      <c r="L57">
+        <v>1.72</v>
+      </c>
+      <c r="M57">
+        <v>3.135132</v>
+      </c>
+      <c r="N57">
+        <v>-1.415132000000001</v>
+      </c>
+      <c r="O57">
+        <v>-0.3537830000000001</v>
+      </c>
+      <c r="P57">
+        <v>-1.061349</v>
+      </c>
+      <c r="Q57">
+        <v>-0.3013490000000003</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1153326297183442</v>
+      </c>
+      <c r="T57">
+        <v>1.036373905345245</v>
+      </c>
+      <c r="U57">
+        <v>0.2088</v>
+      </c>
+      <c r="V57">
+        <v>0.1371553095691027</v>
+      </c>
+      <c r="W57">
+        <v>0.1801619713619714</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.5486212382764106</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1526887676223391</v>
+      </c>
+      <c r="C58">
+        <v>-4.892543434687511</v>
+      </c>
+      <c r="D58">
+        <v>9.49945656531249</v>
+      </c>
+      <c r="E58">
+        <v>1.888000000000002</v>
+      </c>
+      <c r="F58">
+        <v>15.288</v>
+      </c>
+      <c r="G58">
+        <v>0.896</v>
+      </c>
+      <c r="H58">
+        <v>13.9</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>2.48</v>
+      </c>
+      <c r="K58">
+        <v>0.76</v>
+      </c>
+      <c r="L58">
+        <v>1.72</v>
+      </c>
+      <c r="M58">
+        <v>3.1921344</v>
+      </c>
+      <c r="N58">
+        <v>-1.472134400000001</v>
+      </c>
+      <c r="O58">
+        <v>-0.3680336000000001</v>
+      </c>
+      <c r="P58">
+        <v>-1.1041008</v>
+      </c>
+      <c r="Q58">
+        <v>-0.3441008000000003</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1170720076664883</v>
+      </c>
+      <c r="T58">
+        <v>1.059927857739455</v>
+      </c>
+      <c r="U58">
+        <v>0.2088</v>
+      </c>
+      <c r="V58">
+        <v>0.1347061076125115</v>
+      </c>
+      <c r="W58">
+        <v>0.1806733647305076</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.5388244304500461</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1543887676223391</v>
+      </c>
+      <c r="C59">
+        <v>-5.305254900543732</v>
+      </c>
+      <c r="D59">
+        <v>9.359745099456269</v>
+      </c>
+      <c r="E59">
+        <v>2.161000000000001</v>
+      </c>
+      <c r="F59">
+        <v>15.561</v>
+      </c>
+      <c r="G59">
+        <v>0.896</v>
+      </c>
+      <c r="H59">
+        <v>13.9</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>2.48</v>
+      </c>
+      <c r="K59">
+        <v>0.76</v>
+      </c>
+      <c r="L59">
+        <v>1.72</v>
+      </c>
+      <c r="M59">
+        <v>3.2491368</v>
+      </c>
+      <c r="N59">
+        <v>-1.529136800000001</v>
+      </c>
+      <c r="O59">
+        <v>-0.3822842000000001</v>
+      </c>
+      <c r="P59">
+        <v>-1.1468526</v>
+      </c>
+      <c r="Q59">
+        <v>-0.3868526000000003</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1188922869145462</v>
+      </c>
+      <c r="T59">
+        <v>1.084577342803164</v>
+      </c>
+      <c r="U59">
+        <v>0.2088</v>
+      </c>
+      <c r="V59">
+        <v>0.132342842566678</v>
+      </c>
+      <c r="W59">
+        <v>0.1811668144720777</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.529371370266712</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1560887676223391</v>
+      </c>
+      <c r="C60">
+        <v>-5.713916370875735</v>
+      </c>
+      <c r="D60">
+        <v>9.224083629124264</v>
+      </c>
+      <c r="E60">
+        <v>2.433999999999999</v>
+      </c>
+      <c r="F60">
+        <v>15.834</v>
+      </c>
+      <c r="G60">
+        <v>0.896</v>
+      </c>
+      <c r="H60">
+        <v>13.9</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>2.48</v>
+      </c>
+      <c r="K60">
+        <v>0.76</v>
+      </c>
+      <c r="L60">
+        <v>1.72</v>
+      </c>
+      <c r="M60">
+        <v>3.3061392</v>
+      </c>
+      <c r="N60">
+        <v>-1.5861392</v>
+      </c>
+      <c r="O60">
+        <v>-0.3965348</v>
+      </c>
+      <c r="P60">
+        <v>-1.1896044</v>
+      </c>
+      <c r="Q60">
+        <v>-0.4296044000000001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1207992461267973</v>
+      </c>
+      <c r="T60">
+        <v>1.110400612869905</v>
+      </c>
+      <c r="U60">
+        <v>0.2088</v>
+      </c>
+      <c r="V60">
+        <v>0.1300610694189767</v>
+      </c>
+      <c r="W60">
+        <v>0.1816432487053177</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.5202442776759066</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1577887676223391</v>
+      </c>
+      <c r="C61">
+        <v>-6.118701433305171</v>
+      </c>
+      <c r="D61">
+        <v>9.092298566694827</v>
+      </c>
+      <c r="E61">
+        <v>2.706999999999999</v>
+      </c>
+      <c r="F61">
+        <v>16.107</v>
+      </c>
+      <c r="G61">
+        <v>0.896</v>
+      </c>
+      <c r="H61">
+        <v>13.9</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>2.48</v>
+      </c>
+      <c r="K61">
+        <v>0.76</v>
+      </c>
+      <c r="L61">
+        <v>1.72</v>
+      </c>
+      <c r="M61">
+        <v>3.3631416</v>
+      </c>
+      <c r="N61">
+        <v>-1.6431416</v>
+      </c>
+      <c r="O61">
+        <v>-0.4107854</v>
+      </c>
+      <c r="P61">
+        <v>-1.2323562</v>
+      </c>
+      <c r="Q61">
+        <v>-0.4723562000000001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.122799227739646</v>
+      </c>
+      <c r="T61">
+        <v>1.13748355464722</v>
+      </c>
+      <c r="U61">
+        <v>0.2088</v>
+      </c>
+      <c r="V61">
+        <v>0.1278566445135703</v>
+      </c>
+      <c r="W61">
+        <v>0.1821035326255665</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.5114265780542812</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1594887676223391</v>
+      </c>
+      <c r="C62">
+        <v>-6.519773894959174</v>
+      </c>
+      <c r="D62">
+        <v>8.964226105040824</v>
+      </c>
+      <c r="E62">
+        <v>2.979999999999999</v>
+      </c>
+      <c r="F62">
+        <v>16.38</v>
+      </c>
+      <c r="G62">
+        <v>0.896</v>
+      </c>
+      <c r="H62">
+        <v>13.9</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>2.48</v>
+      </c>
+      <c r="K62">
+        <v>0.76</v>
+      </c>
+      <c r="L62">
+        <v>1.72</v>
+      </c>
+      <c r="M62">
+        <v>3.420144</v>
+      </c>
+      <c r="N62">
+        <v>-1.700144</v>
+      </c>
+      <c r="O62">
+        <v>-0.425036</v>
+      </c>
+      <c r="P62">
+        <v>-1.275108</v>
+      </c>
+      <c r="Q62">
+        <v>-0.5151080000000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1248992084331371</v>
+      </c>
+      <c r="T62">
+        <v>1.1659206435134</v>
+      </c>
+      <c r="U62">
+        <v>0.2088</v>
+      </c>
+      <c r="V62">
+        <v>0.1257257004383441</v>
+      </c>
+      <c r="W62">
+        <v>0.1825484737484738</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.5029028017533764</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1798417752950633</v>
+      </c>
+      <c r="C63">
+        <v>-8.086354908912254</v>
+      </c>
+      <c r="D63">
+        <v>7.670645091087744</v>
+      </c>
+      <c r="E63">
+        <v>3.252999999999998</v>
+      </c>
+      <c r="F63">
+        <v>16.653</v>
+      </c>
+      <c r="G63">
+        <v>0.896</v>
+      </c>
+      <c r="H63">
+        <v>13.9</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>2.48</v>
+      </c>
+      <c r="K63">
+        <v>0.76</v>
+      </c>
+      <c r="L63">
+        <v>1.72</v>
+      </c>
+      <c r="M63">
+        <v>3.9767364</v>
+      </c>
+      <c r="N63">
+        <v>-2.2567364</v>
+      </c>
+      <c r="O63">
+        <v>-0.5641841000000001</v>
+      </c>
+      <c r="P63">
+        <v>-1.6925523</v>
+      </c>
+      <c r="Q63">
+        <v>-0.9325523000000002</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1280120283230232</v>
+      </c>
+      <c r="T63">
+        <v>1.20807319096656</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.1081288666756992</v>
+      </c>
+      <c r="W63">
+        <v>0.212978826637843</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.4325154667027967</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1818417752950633</v>
+      </c>
+      <c r="C64">
+        <v>-8.466605326844572</v>
+      </c>
+      <c r="D64">
+        <v>7.56339467315543</v>
+      </c>
+      <c r="E64">
+        <v>3.526000000000002</v>
+      </c>
+      <c r="F64">
+        <v>16.926</v>
+      </c>
+      <c r="G64">
+        <v>0.896</v>
+      </c>
+      <c r="H64">
+        <v>13.9</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>2.48</v>
+      </c>
+      <c r="K64">
+        <v>0.76</v>
+      </c>
+      <c r="L64">
+        <v>1.72</v>
+      </c>
+      <c r="M64">
+        <v>4.041928800000001</v>
+      </c>
+      <c r="N64">
+        <v>-2.321928800000001</v>
+      </c>
+      <c r="O64">
+        <v>-0.5804822000000003</v>
+      </c>
+      <c r="P64">
+        <v>-1.741446600000001</v>
+      </c>
+      <c r="Q64">
+        <v>-0.9814466000000008</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1303597132788922</v>
+      </c>
+      <c r="T64">
+        <v>1.239864590728837</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.1063848526970589</v>
+      </c>
+      <c r="W64">
+        <v>0.2133952971759424</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.4255394107882354</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1838417752950633</v>
+      </c>
+      <c r="C65">
+        <v>-8.843897964710715</v>
+      </c>
+      <c r="D65">
+        <v>7.459102035289286</v>
+      </c>
+      <c r="E65">
+        <v>3.799000000000001</v>
+      </c>
+      <c r="F65">
+        <v>17.199</v>
+      </c>
+      <c r="G65">
+        <v>0.896</v>
+      </c>
+      <c r="H65">
+        <v>13.9</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>2.48</v>
+      </c>
+      <c r="K65">
+        <v>0.76</v>
+      </c>
+      <c r="L65">
+        <v>1.72</v>
+      </c>
+      <c r="M65">
+        <v>4.107121200000001</v>
+      </c>
+      <c r="N65">
+        <v>-2.387121200000001</v>
+      </c>
+      <c r="O65">
+        <v>-0.5967803000000003</v>
+      </c>
+      <c r="P65">
+        <v>-1.790340900000001</v>
+      </c>
+      <c r="Q65">
+        <v>-1.030340900000001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1328343001242677</v>
+      </c>
+      <c r="T65">
+        <v>1.27337444453232</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.10469620424155</v>
+      </c>
+      <c r="W65">
+        <v>0.2137985464271179</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.4187848169662</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1858417752950633</v>
+      </c>
+      <c r="C66">
+        <v>-9.218353513928909</v>
+      </c>
+      <c r="D66">
+        <v>7.357646486071093</v>
+      </c>
+      <c r="E66">
+        <v>4.072000000000001</v>
+      </c>
+      <c r="F66">
+        <v>17.472</v>
+      </c>
+      <c r="G66">
+        <v>0.896</v>
+      </c>
+      <c r="H66">
+        <v>13.9</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>2.48</v>
+      </c>
+      <c r="K66">
+        <v>0.76</v>
+      </c>
+      <c r="L66">
+        <v>1.72</v>
+      </c>
+      <c r="M66">
+        <v>4.172313600000001</v>
+      </c>
+      <c r="N66">
+        <v>-2.452313600000001</v>
+      </c>
+      <c r="O66">
+        <v>-0.6130784000000002</v>
+      </c>
+      <c r="P66">
+        <v>-1.839235200000001</v>
+      </c>
+      <c r="Q66">
+        <v>-1.079235200000001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1354463640166085</v>
+      </c>
+      <c r="T66">
+        <v>1.30874595688044</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.1030603260502758</v>
+      </c>
+      <c r="W66">
+        <v>0.2141891941391942</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.4122413042011031</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1878417752950633</v>
+      </c>
+      <c r="C67">
+        <v>-9.59008618765753</v>
+      </c>
+      <c r="D67">
+        <v>7.258913812342471</v>
+      </c>
+      <c r="E67">
+        <v>4.345000000000001</v>
+      </c>
+      <c r="F67">
+        <v>17.745</v>
+      </c>
+      <c r="G67">
+        <v>0.896</v>
+      </c>
+      <c r="H67">
+        <v>13.9</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>2.48</v>
+      </c>
+      <c r="K67">
+        <v>0.76</v>
+      </c>
+      <c r="L67">
+        <v>1.72</v>
+      </c>
+      <c r="M67">
+        <v>4.237506000000001</v>
+      </c>
+      <c r="N67">
+        <v>-2.517506000000001</v>
+      </c>
+      <c r="O67">
+        <v>-0.6293765000000002</v>
+      </c>
+      <c r="P67">
+        <v>-1.888129500000001</v>
+      </c>
+      <c r="Q67">
+        <v>-1.128129500000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1382076887027973</v>
+      </c>
+      <c r="T67">
+        <v>1.346138698505595</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.1014747825725792</v>
+      </c>
+      <c r="W67">
+        <v>0.2145678219216681</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.4058991302903169</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1898417752950633</v>
+      </c>
+      <c r="C68">
+        <v>-9.959204149700309</v>
+      </c>
+      <c r="D68">
+        <v>7.162795850299692</v>
+      </c>
+      <c r="E68">
+        <v>4.618</v>
+      </c>
+      <c r="F68">
+        <v>18.018</v>
+      </c>
+      <c r="G68">
+        <v>0.896</v>
+      </c>
+      <c r="H68">
+        <v>13.9</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>2.48</v>
+      </c>
+      <c r="K68">
+        <v>0.76</v>
+      </c>
+      <c r="L68">
+        <v>1.72</v>
+      </c>
+      <c r="M68">
+        <v>4.302698400000001</v>
+      </c>
+      <c r="N68">
+        <v>-2.582698400000001</v>
+      </c>
+      <c r="O68">
+        <v>-0.6456746000000002</v>
+      </c>
+      <c r="P68">
+        <v>-1.937023800000001</v>
+      </c>
+      <c r="Q68">
+        <v>-1.177023800000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1411314442528796</v>
+      </c>
+      <c r="T68">
+        <v>1.385731013167524</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.09993728586693409</v>
+      </c>
+      <c r="W68">
+        <v>0.2149349761349762</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3997491434677363</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1918417752950633</v>
+      </c>
+      <c r="C69">
+        <v>-10.32580990978104</v>
+      </c>
+      <c r="D69">
+        <v>7.069190090218957</v>
+      </c>
+      <c r="E69">
+        <v>4.891</v>
+      </c>
+      <c r="F69">
+        <v>18.291</v>
+      </c>
+      <c r="G69">
+        <v>0.896</v>
+      </c>
+      <c r="H69">
+        <v>13.9</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>2.48</v>
+      </c>
+      <c r="K69">
+        <v>0.76</v>
+      </c>
+      <c r="L69">
+        <v>1.72</v>
+      </c>
+      <c r="M69">
+        <v>4.367890800000001</v>
+      </c>
+      <c r="N69">
+        <v>-2.647890800000001</v>
+      </c>
+      <c r="O69">
+        <v>-0.6619727000000002</v>
+      </c>
+      <c r="P69">
+        <v>-1.985918100000001</v>
+      </c>
+      <c r="Q69">
+        <v>-1.225918100000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1442323971090275</v>
+      </c>
+      <c r="T69">
+        <v>1.427722862051389</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.09844568458533806</v>
+      </c>
+      <c r="W69">
+        <v>0.2152911705210213</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3937827383413522</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1938417752950633</v>
+      </c>
+      <c r="C70">
+        <v>-10.69000068822466</v>
+      </c>
+      <c r="D70">
+        <v>6.977999311775336</v>
+      </c>
+      <c r="E70">
+        <v>5.164</v>
+      </c>
+      <c r="F70">
+        <v>18.564</v>
+      </c>
+      <c r="G70">
+        <v>0.896</v>
+      </c>
+      <c r="H70">
+        <v>13.9</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>2.48</v>
+      </c>
+      <c r="K70">
+        <v>0.76</v>
+      </c>
+      <c r="L70">
+        <v>1.72</v>
+      </c>
+      <c r="M70">
+        <v>4.4330832</v>
+      </c>
+      <c r="N70">
+        <v>-2.713083200000001</v>
+      </c>
+      <c r="O70">
+        <v>-0.6782708000000002</v>
+      </c>
+      <c r="P70">
+        <v>-2.034812400000001</v>
+      </c>
+      <c r="Q70">
+        <v>-1.274812400000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1475271595186846</v>
+      </c>
+      <c r="T70">
+        <v>1.472339201490495</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.09699795392967132</v>
+      </c>
+      <c r="W70">
+        <v>0.2156368886015945</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3879918157186852</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1958417752950633</v>
+      </c>
+      <c r="C71">
+        <v>-11.05186875277201</v>
+      </c>
+      <c r="D71">
+        <v>6.889131247227994</v>
+      </c>
+      <c r="E71">
+        <v>5.437000000000003</v>
+      </c>
+      <c r="F71">
+        <v>18.837</v>
+      </c>
+      <c r="G71">
+        <v>0.896</v>
+      </c>
+      <c r="H71">
+        <v>13.9</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>2.48</v>
+      </c>
+      <c r="K71">
+        <v>0.76</v>
+      </c>
+      <c r="L71">
+        <v>1.72</v>
+      </c>
+      <c r="M71">
+        <v>4.498275600000001</v>
+      </c>
+      <c r="N71">
+        <v>-2.778275600000002</v>
+      </c>
+      <c r="O71">
+        <v>-0.6945689000000004</v>
+      </c>
+      <c r="P71">
+        <v>-2.083706700000001</v>
+      </c>
+      <c r="Q71">
+        <v>-1.323706700000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1510344872450937</v>
+      </c>
+      <c r="T71">
+        <v>1.519834014441801</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.09559218648141521</v>
+      </c>
+      <c r="W71">
+        <v>0.2159725858682381</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3823687459256607</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1978417752950633</v>
+      </c>
+      <c r="C72">
+        <v>-11.41150172998126</v>
+      </c>
+      <c r="D72">
+        <v>6.802498270018742</v>
+      </c>
+      <c r="E72">
+        <v>5.710000000000003</v>
+      </c>
+      <c r="F72">
+        <v>19.11</v>
+      </c>
+      <c r="G72">
+        <v>0.896</v>
+      </c>
+      <c r="H72">
+        <v>13.9</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>2.48</v>
+      </c>
+      <c r="K72">
+        <v>0.76</v>
+      </c>
+      <c r="L72">
+        <v>1.72</v>
+      </c>
+      <c r="M72">
+        <v>4.563468000000001</v>
+      </c>
+      <c r="N72">
+        <v>-2.843468000000001</v>
+      </c>
+      <c r="O72">
+        <v>-0.7108670000000004</v>
+      </c>
+      <c r="P72">
+        <v>-2.132601000000001</v>
+      </c>
+      <c r="Q72">
+        <v>-1.372601000000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1547756368199302</v>
+      </c>
+      <c r="T72">
+        <v>1.570495148256528</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.09422658381739499</v>
+      </c>
+      <c r="W72">
+        <v>0.2162986917844061</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.37690633526958</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1998417752950633</v>
+      </c>
+      <c r="C73">
+        <v>-11.7689828934254</v>
+      </c>
+      <c r="D73">
+        <v>6.7180171065746</v>
+      </c>
+      <c r="E73">
+        <v>5.982999999999999</v>
+      </c>
+      <c r="F73">
+        <v>19.383</v>
+      </c>
+      <c r="G73">
+        <v>0.896</v>
+      </c>
+      <c r="H73">
+        <v>13.9</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>2.48</v>
+      </c>
+      <c r="K73">
+        <v>0.76</v>
+      </c>
+      <c r="L73">
+        <v>1.72</v>
+      </c>
+      <c r="M73">
+        <v>4.6286604</v>
+      </c>
+      <c r="N73">
+        <v>-2.9086604</v>
+      </c>
+      <c r="O73">
+        <v>-0.7271651000000001</v>
+      </c>
+      <c r="P73">
+        <v>-2.1814953</v>
+      </c>
+      <c r="Q73">
+        <v>-1.4214953</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1587747967102726</v>
+      </c>
+      <c r="T73">
+        <v>1.624650153368822</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.09289944883405142</v>
+      </c>
+      <c r="W73">
+        <v>0.2166156116184285</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3715977953362056</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2018417752950633</v>
+      </c>
+      <c r="C74">
+        <v>-12.1243914306781</v>
+      </c>
+      <c r="D74">
+        <v>6.635608569321902</v>
+      </c>
+      <c r="E74">
+        <v>6.255999999999998</v>
+      </c>
+      <c r="F74">
+        <v>19.656</v>
+      </c>
+      <c r="G74">
+        <v>0.896</v>
+      </c>
+      <c r="H74">
+        <v>13.9</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>2.48</v>
+      </c>
+      <c r="K74">
+        <v>0.76</v>
+      </c>
+      <c r="L74">
+        <v>1.72</v>
+      </c>
+      <c r="M74">
+        <v>4.6938528</v>
+      </c>
+      <c r="N74">
+        <v>-2.9738528</v>
+      </c>
+      <c r="O74">
+        <v>-0.7434632000000001</v>
+      </c>
+      <c r="P74">
+        <v>-2.230389600000001</v>
+      </c>
+      <c r="Q74">
+        <v>-1.470389600000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1630596108784966</v>
+      </c>
+      <c r="T74">
+        <v>1.682673373131994</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.09160917871135627</v>
+      </c>
+      <c r="W74">
+        <v>0.2169237281237281</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3664367148454249</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2038417752950633</v>
+      </c>
+      <c r="C75">
+        <v>-12.47780269088732</v>
+      </c>
+      <c r="D75">
+        <v>6.555197309112677</v>
+      </c>
+      <c r="E75">
+        <v>6.528999999999998</v>
+      </c>
+      <c r="F75">
+        <v>19.929</v>
+      </c>
+      <c r="G75">
+        <v>0.896</v>
+      </c>
+      <c r="H75">
+        <v>13.9</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>2.48</v>
+      </c>
+      <c r="K75">
+        <v>0.76</v>
+      </c>
+      <c r="L75">
+        <v>1.72</v>
+      </c>
+      <c r="M75">
+        <v>4.7590452</v>
+      </c>
+      <c r="N75">
+        <v>-3.0390452</v>
+      </c>
+      <c r="O75">
+        <v>-0.7597613000000001</v>
+      </c>
+      <c r="P75">
+        <v>-2.2792839</v>
+      </c>
+      <c r="Q75">
+        <v>-1.5192839</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1676618186888113</v>
+      </c>
+      <c r="T75">
+        <v>1.744994609173919</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.09035425845503631</v>
+      </c>
+      <c r="W75">
+        <v>0.2172234030809373</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3614170338201452</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2058417752950633</v>
+      </c>
+      <c r="C76">
+        <v>-12.82928841456373</v>
+      </c>
+      <c r="D76">
+        <v>6.476711585436266</v>
+      </c>
+      <c r="E76">
+        <v>6.802000000000001</v>
+      </c>
+      <c r="F76">
+        <v>20.202</v>
+      </c>
+      <c r="G76">
+        <v>0.896</v>
+      </c>
+      <c r="H76">
+        <v>13.9</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>2.48</v>
+      </c>
+      <c r="K76">
+        <v>0.76</v>
+      </c>
+      <c r="L76">
+        <v>1.72</v>
+      </c>
+      <c r="M76">
+        <v>4.824237600000001</v>
+      </c>
+      <c r="N76">
+        <v>-3.104237600000001</v>
+      </c>
+      <c r="O76">
+        <v>-0.7760594000000003</v>
+      </c>
+      <c r="P76">
+        <v>-2.328178200000001</v>
+      </c>
+      <c r="Q76">
+        <v>-1.568178200000001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1726180424845348</v>
+      </c>
+      <c r="T76">
+        <v>1.812109786449839</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.08913325496240067</v>
+      </c>
+      <c r="W76">
+        <v>0.2175149787149787</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3565330198496026</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2078417752950633</v>
+      </c>
+      <c r="C77">
+        <v>-13.17891694705674</v>
+      </c>
+      <c r="D77">
+        <v>6.400083052943265</v>
+      </c>
+      <c r="E77">
+        <v>7.075000000000001</v>
+      </c>
+      <c r="F77">
+        <v>20.475</v>
+      </c>
+      <c r="G77">
+        <v>0.896</v>
+      </c>
+      <c r="H77">
+        <v>13.9</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>2.48</v>
+      </c>
+      <c r="K77">
+        <v>0.76</v>
+      </c>
+      <c r="L77">
+        <v>1.72</v>
+      </c>
+      <c r="M77">
+        <v>4.889430000000001</v>
+      </c>
+      <c r="N77">
+        <v>-3.169430000000001</v>
+      </c>
+      <c r="O77">
+        <v>-0.7923575000000003</v>
+      </c>
+      <c r="P77">
+        <v>-2.377072500000001</v>
+      </c>
+      <c r="Q77">
+        <v>-1.617072500000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1779707641839162</v>
+      </c>
+      <c r="T77">
+        <v>1.884594177907833</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.087944811562902</v>
+      </c>
+      <c r="W77">
+        <v>0.217798778998779</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3517792462516079</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2098417752950633</v>
+      </c>
+      <c r="C78">
+        <v>-13.52675343705344</v>
+      </c>
+      <c r="D78">
+        <v>6.325246562946564</v>
+      </c>
+      <c r="E78">
+        <v>7.348000000000001</v>
+      </c>
+      <c r="F78">
+        <v>20.748</v>
+      </c>
+      <c r="G78">
+        <v>0.896</v>
+      </c>
+      <c r="H78">
+        <v>13.9</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>2.48</v>
+      </c>
+      <c r="K78">
+        <v>0.76</v>
+      </c>
+      <c r="L78">
+        <v>1.72</v>
+      </c>
+      <c r="M78">
+        <v>4.954622400000001</v>
+      </c>
+      <c r="N78">
+        <v>-3.234622400000001</v>
+      </c>
+      <c r="O78">
+        <v>-0.8086556000000003</v>
+      </c>
+      <c r="P78">
+        <v>-2.425966800000001</v>
+      </c>
+      <c r="Q78">
+        <v>-1.665966800000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.1837695460249127</v>
+      </c>
+      <c r="T78">
+        <v>1.96311893532066</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.08678764298970593</v>
+      </c>
+      <c r="W78">
+        <v>0.2180751108540583</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3471505719588236</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2118417752950633</v>
+      </c>
+      <c r="C79">
+        <v>-13.87286002131219</v>
+      </c>
+      <c r="D79">
+        <v>6.25213997868781</v>
+      </c>
+      <c r="E79">
+        <v>7.621</v>
+      </c>
+      <c r="F79">
+        <v>21.021</v>
+      </c>
+      <c r="G79">
+        <v>0.896</v>
+      </c>
+      <c r="H79">
+        <v>13.9</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>2.48</v>
+      </c>
+      <c r="K79">
+        <v>0.76</v>
+      </c>
+      <c r="L79">
+        <v>1.72</v>
+      </c>
+      <c r="M79">
+        <v>5.019814800000001</v>
+      </c>
+      <c r="N79">
+        <v>-3.299814800000001</v>
+      </c>
+      <c r="O79">
+        <v>-0.8249537000000002</v>
+      </c>
+      <c r="P79">
+        <v>-2.474861100000001</v>
+      </c>
+      <c r="Q79">
+        <v>-1.714861100000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.1900725697651263</v>
+      </c>
+      <c r="T79">
+        <v>2.048471932508514</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.08566053074308637</v>
+      </c>
+      <c r="W79">
+        <v>0.218344265258551</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3426421229723454</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2138417752950633</v>
+      </c>
+      <c r="C80">
+        <v>-14.21729599673176</v>
+      </c>
+      <c r="D80">
+        <v>6.180704003268242</v>
+      </c>
+      <c r="E80">
+        <v>7.894</v>
+      </c>
+      <c r="F80">
+        <v>21.294</v>
+      </c>
+      <c r="G80">
+        <v>0.896</v>
+      </c>
+      <c r="H80">
+        <v>13.9</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>2.48</v>
+      </c>
+      <c r="K80">
+        <v>0.76</v>
+      </c>
+      <c r="L80">
+        <v>1.72</v>
+      </c>
+      <c r="M80">
+        <v>5.085007200000001</v>
+      </c>
+      <c r="N80">
+        <v>-3.365007200000001</v>
+      </c>
+      <c r="O80">
+        <v>-0.8412518000000002</v>
+      </c>
+      <c r="P80">
+        <v>-2.523755400000001</v>
+      </c>
+      <c r="Q80">
+        <v>-1.763755400000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.1969485956635412</v>
+      </c>
+      <c r="T80">
+        <v>2.141584293077083</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.08456231881048269</v>
+      </c>
+      <c r="W80">
+        <v>0.2186065182680567</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3382492752419307</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2158417752950633</v>
+      </c>
+      <c r="C81">
+        <v>-14.56011798075748</v>
+      </c>
+      <c r="D81">
+        <v>6.110882019242524</v>
+      </c>
+      <c r="E81">
+        <v>8.167</v>
+      </c>
+      <c r="F81">
+        <v>21.567</v>
+      </c>
+      <c r="G81">
+        <v>0.896</v>
+      </c>
+      <c r="H81">
+        <v>13.9</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>2.48</v>
+      </c>
+      <c r="K81">
+        <v>0.76</v>
+      </c>
+      <c r="L81">
+        <v>1.72</v>
+      </c>
+      <c r="M81">
+        <v>5.150199600000001</v>
+      </c>
+      <c r="N81">
+        <v>-3.430199600000001</v>
+      </c>
+      <c r="O81">
+        <v>-0.8575499000000002</v>
+      </c>
+      <c r="P81">
+        <v>-2.5726497</v>
+      </c>
+      <c r="Q81">
+        <v>-1.8126497</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2044794811713289</v>
+      </c>
+      <c r="T81">
+        <v>2.243564497509326</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.08349190971161582</v>
+      </c>
+      <c r="W81">
+        <v>0.2188621319608662</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3339676388464633</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2178417752950634</v>
+      </c>
+      <c r="C82">
+        <v>-14.90138006103647</v>
+      </c>
+      <c r="D82">
+        <v>6.042619938963531</v>
+      </c>
+      <c r="E82">
+        <v>8.440000000000003</v>
+      </c>
+      <c r="F82">
+        <v>21.84</v>
+      </c>
+      <c r="G82">
+        <v>0.896</v>
+      </c>
+      <c r="H82">
+        <v>13.9</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>2.48</v>
+      </c>
+      <c r="K82">
+        <v>0.76</v>
+      </c>
+      <c r="L82">
+        <v>1.72</v>
+      </c>
+      <c r="M82">
+        <v>5.215392000000001</v>
+      </c>
+      <c r="N82">
+        <v>-3.495392000000002</v>
+      </c>
+      <c r="O82">
+        <v>-0.8738480000000004</v>
+      </c>
+      <c r="P82">
+        <v>-2.621544000000001</v>
+      </c>
+      <c r="Q82">
+        <v>-1.861544000000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2127634552298953</v>
+      </c>
+      <c r="T82">
+        <v>2.355742722384792</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.08244826084022061</v>
+      </c>
+      <c r="W82">
+        <v>0.2191113553113553</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3297930433608824</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2198417752950633</v>
+      </c>
+      <c r="C83">
+        <v>-15.24113393515326</v>
+      </c>
+      <c r="D83">
+        <v>5.975866064846742</v>
+      </c>
+      <c r="E83">
+        <v>8.713000000000003</v>
+      </c>
+      <c r="F83">
+        <v>22.113</v>
+      </c>
+      <c r="G83">
+        <v>0.896</v>
+      </c>
+      <c r="H83">
+        <v>13.9</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>2.48</v>
+      </c>
+      <c r="K83">
+        <v>0.76</v>
+      </c>
+      <c r="L83">
+        <v>1.72</v>
+      </c>
+      <c r="M83">
+        <v>5.280584400000001</v>
+      </c>
+      <c r="N83">
+        <v>-3.560584400000002</v>
+      </c>
+      <c r="O83">
+        <v>-0.8901461000000004</v>
+      </c>
+      <c r="P83">
+        <v>-2.670438300000001</v>
+      </c>
+      <c r="Q83">
+        <v>-1.910438300000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2219194265577845</v>
+      </c>
+      <c r="T83">
+        <v>2.479729181457676</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.08143038107676111</v>
+      </c>
+      <c r="W83">
+        <v>0.2193544249988695</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3257215243070444</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2218417752950633</v>
+      </c>
+      <c r="C84">
+        <v>-15.57942904120448</v>
+      </c>
+      <c r="D84">
+        <v>5.910570958795526</v>
+      </c>
+      <c r="E84">
+        <v>8.986000000000002</v>
+      </c>
+      <c r="F84">
+        <v>22.386</v>
+      </c>
+      <c r="G84">
+        <v>0.896</v>
+      </c>
+      <c r="H84">
+        <v>13.9</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>2.48</v>
+      </c>
+      <c r="K84">
+        <v>0.76</v>
+      </c>
+      <c r="L84">
+        <v>1.72</v>
+      </c>
+      <c r="M84">
+        <v>5.345776800000001</v>
+      </c>
+      <c r="N84">
+        <v>-3.625776800000001</v>
+      </c>
+      <c r="O84">
+        <v>-0.9064442000000004</v>
+      </c>
+      <c r="P84">
+        <v>-2.719332600000001</v>
+      </c>
+      <c r="Q84">
+        <v>-1.959332600000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.232092728033217</v>
+      </c>
+      <c r="T84">
+        <v>2.61749191376088</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.08043732764899572</v>
+      </c>
+      <c r="W84">
+        <v>0.2195915661574198</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3217493105959829</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2238417752950633</v>
+      </c>
+      <c r="C85">
+        <v>-15.91631267990574</v>
+      </c>
+      <c r="D85">
+        <v>5.84668732009426</v>
+      </c>
+      <c r="E85">
+        <v>9.259000000000002</v>
+      </c>
+      <c r="F85">
+        <v>22.659</v>
+      </c>
+      <c r="G85">
+        <v>0.896</v>
+      </c>
+      <c r="H85">
+        <v>13.9</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>2.48</v>
+      </c>
+      <c r="K85">
+        <v>0.76</v>
+      </c>
+      <c r="L85">
+        <v>1.72</v>
+      </c>
+      <c r="M85">
+        <v>5.410969200000001</v>
+      </c>
+      <c r="N85">
+        <v>-3.690969200000001</v>
+      </c>
+      <c r="O85">
+        <v>-0.9227423000000003</v>
+      </c>
+      <c r="P85">
+        <v>-2.768226900000001</v>
+      </c>
+      <c r="Q85">
+        <v>-2.008226900000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2434628885057592</v>
+      </c>
+      <c r="T85">
+        <v>2.771462026335049</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.07946820321948976</v>
+      </c>
+      <c r="W85">
+        <v>0.2198229930711859</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.317872812877959</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2258417752950633</v>
+      </c>
+      <c r="C86">
+        <v>-16.25183012886463</v>
+      </c>
+      <c r="D86">
+        <v>5.784169871135375</v>
+      </c>
+      <c r="E86">
+        <v>9.531999999999998</v>
+      </c>
+      <c r="F86">
+        <v>22.932</v>
+      </c>
+      <c r="G86">
+        <v>0.896</v>
+      </c>
+      <c r="H86">
+        <v>13.9</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>2.48</v>
+      </c>
+      <c r="K86">
+        <v>0.76</v>
+      </c>
+      <c r="L86">
+        <v>1.72</v>
+      </c>
+      <c r="M86">
+        <v>5.4761616</v>
+      </c>
+      <c r="N86">
+        <v>-3.7561616</v>
+      </c>
+      <c r="O86">
+        <v>-0.9390404000000001</v>
+      </c>
+      <c r="P86">
+        <v>-2.8171212</v>
+      </c>
+      <c r="Q86">
+        <v>-2.0571212</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2562543190373691</v>
+      </c>
+      <c r="T86">
+        <v>2.944678402980989</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.07852215318116251</v>
+      </c>
+      <c r="W86">
+        <v>0.2200489098203384</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3140886127246501</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2278417752950633</v>
+      </c>
+      <c r="C87">
+        <v>-16.58602474959972</v>
+      </c>
+      <c r="D87">
+        <v>5.722975250400278</v>
+      </c>
+      <c r="E87">
+        <v>9.804999999999998</v>
+      </c>
+      <c r="F87">
+        <v>23.205</v>
+      </c>
+      <c r="G87">
+        <v>0.896</v>
+      </c>
+      <c r="H87">
+        <v>13.9</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>2.48</v>
+      </c>
+      <c r="K87">
+        <v>0.76</v>
+      </c>
+      <c r="L87">
+        <v>1.72</v>
+      </c>
+      <c r="M87">
+        <v>5.541354</v>
+      </c>
+      <c r="N87">
+        <v>-3.821354</v>
+      </c>
+      <c r="O87">
+        <v>-0.9553385000000001</v>
+      </c>
+      <c r="P87">
+        <v>-2.8660155</v>
+      </c>
+      <c r="Q87">
+        <v>-2.106015500000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.2707512736398603</v>
+      </c>
+      <c r="T87">
+        <v>3.140990296513055</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.07759836314373707</v>
+      </c>
+      <c r="W87">
+        <v>0.2202695108812756</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3103934525749482</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2298417752950633</v>
+      </c>
+      <c r="C88">
+        <v>-16.91893808783751</v>
+      </c>
+      <c r="D88">
+        <v>5.663061912162492</v>
+      </c>
+      <c r="E88">
+        <v>10.078</v>
+      </c>
+      <c r="F88">
+        <v>23.478</v>
+      </c>
+      <c r="G88">
+        <v>0.896</v>
+      </c>
+      <c r="H88">
+        <v>13.9</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>2.48</v>
+      </c>
+      <c r="K88">
+        <v>0.76</v>
+      </c>
+      <c r="L88">
+        <v>1.72</v>
+      </c>
+      <c r="M88">
+        <v>5.606546400000001</v>
+      </c>
+      <c r="N88">
+        <v>-3.886546400000001</v>
+      </c>
+      <c r="O88">
+        <v>-0.9716366000000003</v>
+      </c>
+      <c r="P88">
+        <v>-2.914909800000001</v>
+      </c>
+      <c r="Q88">
+        <v>-2.154909800000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.2873192217569932</v>
+      </c>
+      <c r="T88">
+        <v>3.365346746263987</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.07669605659555406</v>
+      </c>
+      <c r="W88">
+        <v>0.2204849816849817</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3067842263822163</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2318417752950633</v>
+      </c>
+      <c r="C89">
+        <v>-17.25060996757449</v>
+      </c>
+      <c r="D89">
+        <v>5.60439003242551</v>
+      </c>
+      <c r="E89">
+        <v>10.351</v>
+      </c>
+      <c r="F89">
+        <v>23.751</v>
+      </c>
+      <c r="G89">
+        <v>0.896</v>
+      </c>
+      <c r="H89">
+        <v>13.9</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>2.48</v>
+      </c>
+      <c r="K89">
+        <v>0.76</v>
+      </c>
+      <c r="L89">
+        <v>1.72</v>
+      </c>
+      <c r="M89">
+        <v>5.671738800000001</v>
+      </c>
+      <c r="N89">
+        <v>-3.951738800000001</v>
+      </c>
+      <c r="O89">
+        <v>-0.9879347000000003</v>
+      </c>
+      <c r="P89">
+        <v>-2.963804100000001</v>
+      </c>
+      <c r="Q89">
+        <v>-2.203804100000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3064360849690696</v>
+      </c>
+      <c r="T89">
+        <v>3.624219572899679</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.07581449272663966</v>
+      </c>
+      <c r="W89">
+        <v>0.2206954991368785</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3032579709065586</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2338417752950633</v>
+      </c>
+      <c r="C90">
+        <v>-17.58107857935212</v>
+      </c>
+      <c r="D90">
+        <v>5.546921420647884</v>
+      </c>
+      <c r="E90">
+        <v>10.624</v>
+      </c>
+      <c r="F90">
+        <v>24.024</v>
+      </c>
+      <c r="G90">
+        <v>0.896</v>
+      </c>
+      <c r="H90">
+        <v>13.9</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>2.48</v>
+      </c>
+      <c r="K90">
+        <v>0.76</v>
+      </c>
+      <c r="L90">
+        <v>1.72</v>
+      </c>
+      <c r="M90">
+        <v>5.736931200000001</v>
+      </c>
+      <c r="N90">
+        <v>-4.016931200000001</v>
+      </c>
+      <c r="O90">
+        <v>-1.0042328</v>
+      </c>
+      <c r="P90">
+        <v>-3.012698400000001</v>
+      </c>
+      <c r="Q90">
+        <v>-2.252698400000001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3287390920498254</v>
+      </c>
+      <c r="T90">
+        <v>3.926237870641319</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.07495296440020056</v>
+      </c>
+      <c r="W90">
+        <v>0.2209012321012321</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2998118576008022</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2358417752950633</v>
+      </c>
+      <c r="C91">
+        <v>-17.91038056315572</v>
+      </c>
+      <c r="D91">
+        <v>5.490619436844282</v>
+      </c>
+      <c r="E91">
+        <v>10.897</v>
+      </c>
+      <c r="F91">
+        <v>24.297</v>
+      </c>
+      <c r="G91">
+        <v>0.896</v>
+      </c>
+      <c r="H91">
+        <v>13.9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>2.48</v>
+      </c>
+      <c r="K91">
+        <v>0.76</v>
+      </c>
+      <c r="L91">
+        <v>1.72</v>
+      </c>
+      <c r="M91">
+        <v>5.802123600000001</v>
+      </c>
+      <c r="N91">
+        <v>-4.082123600000001</v>
+      </c>
+      <c r="O91">
+        <v>-1.0205309</v>
+      </c>
+      <c r="P91">
+        <v>-3.061592700000001</v>
+      </c>
+      <c r="Q91">
+        <v>-2.3015927</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.3550971913270823</v>
+      </c>
+      <c r="T91">
+        <v>4.283168586154167</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.07411079626087247</v>
+      </c>
+      <c r="W91">
+        <v>0.2211023418529037</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2964431850434899</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2378417752950633</v>
+      </c>
+      <c r="C92">
+        <v>-18.23855108631554</v>
+      </c>
+      <c r="D92">
+        <v>5.435448913684459</v>
+      </c>
+      <c r="E92">
+        <v>11.17</v>
+      </c>
+      <c r="F92">
+        <v>24.57</v>
+      </c>
+      <c r="G92">
+        <v>0.896</v>
+      </c>
+      <c r="H92">
+        <v>13.9</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>2.48</v>
+      </c>
+      <c r="K92">
+        <v>0.76</v>
+      </c>
+      <c r="L92">
+        <v>1.72</v>
+      </c>
+      <c r="M92">
+        <v>5.867316000000001</v>
+      </c>
+      <c r="N92">
+        <v>-4.147316000000001</v>
+      </c>
+      <c r="O92">
+        <v>-1.036829</v>
+      </c>
+      <c r="P92">
+        <v>-3.110487000000001</v>
+      </c>
+      <c r="Q92">
+        <v>-2.350487000000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.3867269104597906</v>
+      </c>
+      <c r="T92">
+        <v>4.711485444769584</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.073287342969085</v>
+      </c>
+      <c r="W92">
+        <v>0.2212989824989825</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2931493718763399</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2398417752950633</v>
+      </c>
+      <c r="C93">
+        <v>-18.56562391675794</v>
+      </c>
+      <c r="D93">
+        <v>5.38137608324206</v>
+      </c>
+      <c r="E93">
+        <v>11.443</v>
+      </c>
+      <c r="F93">
+        <v>24.843</v>
+      </c>
+      <c r="G93">
+        <v>0.896</v>
+      </c>
+      <c r="H93">
+        <v>13.9</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>2.48</v>
+      </c>
+      <c r="K93">
+        <v>0.76</v>
+      </c>
+      <c r="L93">
+        <v>1.72</v>
+      </c>
+      <c r="M93">
+        <v>5.932508400000001</v>
+      </c>
+      <c r="N93">
+        <v>-4.212508400000001</v>
+      </c>
+      <c r="O93">
+        <v>-1.0531271</v>
+      </c>
+      <c r="P93">
+        <v>-3.159381300000001</v>
+      </c>
+      <c r="Q93">
+        <v>-2.399381300000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.425385456066434</v>
+      </c>
+      <c r="T93">
+        <v>5.23498382752176</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.07248198755184231</v>
+      </c>
+      <c r="W93">
+        <v>0.2214913013726201</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2899279502073692</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2418417752950633</v>
+      </c>
+      <c r="C94">
+        <v>-18.89163149192736</v>
+      </c>
+      <c r="D94">
+        <v>5.328368508072645</v>
+      </c>
+      <c r="E94">
+        <v>11.716</v>
+      </c>
+      <c r="F94">
+        <v>25.116</v>
+      </c>
+      <c r="G94">
+        <v>0.896</v>
+      </c>
+      <c r="H94">
+        <v>13.9</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>2.48</v>
+      </c>
+      <c r="K94">
+        <v>0.76</v>
+      </c>
+      <c r="L94">
+        <v>1.72</v>
+      </c>
+      <c r="M94">
+        <v>5.997700800000001</v>
+      </c>
+      <c r="N94">
+        <v>-4.277700800000002</v>
+      </c>
+      <c r="O94">
+        <v>-1.0694252</v>
+      </c>
+      <c r="P94">
+        <v>-3.208275600000001</v>
+      </c>
+      <c r="Q94">
+        <v>-2.448275600000001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.4737086380747384</v>
+      </c>
+      <c r="T94">
+        <v>5.889356805961982</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.07169413986106141</v>
+      </c>
+      <c r="W94">
+        <v>0.2216794394011785</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2867765594442456</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2438417752950633</v>
+      </c>
+      <c r="C95">
+        <v>-19.21660498367464</v>
+      </c>
+      <c r="D95">
+        <v>5.276395016325369</v>
+      </c>
+      <c r="E95">
+        <v>11.989</v>
+      </c>
+      <c r="F95">
+        <v>25.389</v>
+      </c>
+      <c r="G95">
+        <v>0.896</v>
+      </c>
+      <c r="H95">
+        <v>13.9</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>2.48</v>
+      </c>
+      <c r="K95">
+        <v>0.76</v>
+      </c>
+      <c r="L95">
+        <v>1.72</v>
+      </c>
+      <c r="M95">
+        <v>6.062893200000001</v>
+      </c>
+      <c r="N95">
+        <v>-4.342893200000002</v>
+      </c>
+      <c r="O95">
+        <v>-1.0857233</v>
+      </c>
+      <c r="P95">
+        <v>-3.257169900000001</v>
+      </c>
+      <c r="Q95">
+        <v>-2.497169900000001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.5358384435139868</v>
+      </c>
+      <c r="T95">
+        <v>6.73069349252798</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.07092323513137258</v>
+      </c>
+      <c r="W95">
+        <v>0.2218635314506282</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2836929405254903</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2458417752950633</v>
+      </c>
+      <c r="C96">
+        <v>-19.54057435938449</v>
+      </c>
+      <c r="D96">
+        <v>5.225425640615508</v>
+      </c>
+      <c r="E96">
+        <v>12.262</v>
+      </c>
+      <c r="F96">
+        <v>25.662</v>
+      </c>
+      <c r="G96">
+        <v>0.896</v>
+      </c>
+      <c r="H96">
+        <v>13.9</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>2.48</v>
+      </c>
+      <c r="K96">
+        <v>0.76</v>
+      </c>
+      <c r="L96">
+        <v>1.72</v>
+      </c>
+      <c r="M96">
+        <v>6.128085600000001</v>
+      </c>
+      <c r="N96">
+        <v>-4.408085600000001</v>
+      </c>
+      <c r="O96">
+        <v>-1.1020214</v>
+      </c>
+      <c r="P96">
+        <v>-3.306064200000001</v>
+      </c>
+      <c r="Q96">
+        <v>-2.546064200000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.6186781840996514</v>
+      </c>
+      <c r="T96">
+        <v>7.852475741282644</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.070168732629975</v>
+      </c>
+      <c r="W96">
+        <v>0.222043706647962</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2806749305199</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2478417752950633</v>
+      </c>
+      <c r="C97">
+        <v>-19.86356843959396</v>
+      </c>
+      <c r="D97">
+        <v>5.175431560406039</v>
+      </c>
+      <c r="E97">
+        <v>12.535</v>
+      </c>
+      <c r="F97">
+        <v>25.935</v>
+      </c>
+      <c r="G97">
+        <v>0.896</v>
+      </c>
+      <c r="H97">
+        <v>13.9</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>2.48</v>
+      </c>
+      <c r="K97">
+        <v>0.76</v>
+      </c>
+      <c r="L97">
+        <v>1.72</v>
+      </c>
+      <c r="M97">
+        <v>6.193278000000001</v>
+      </c>
+      <c r="N97">
+        <v>-4.473278000000001</v>
+      </c>
+      <c r="O97">
+        <v>-1.1183195</v>
+      </c>
+      <c r="P97">
+        <v>-3.354958500000001</v>
+      </c>
+      <c r="Q97">
+        <v>-2.594958500000002</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.7346538209195819</v>
+      </c>
+      <c r="T97">
+        <v>9.422970889539178</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.06943011439176473</v>
+      </c>
+      <c r="W97">
+        <v>0.2222200886832466</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2777204575670589</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2498417752950633</v>
+      </c>
+      <c r="C98">
+        <v>-20.18561495233458</v>
+      </c>
+      <c r="D98">
+        <v>5.126385047665419</v>
+      </c>
+      <c r="E98">
+        <v>12.808</v>
+      </c>
+      <c r="F98">
+        <v>26.208</v>
+      </c>
+      <c r="G98">
+        <v>0.896</v>
+      </c>
+      <c r="H98">
+        <v>13.9</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>2.48</v>
+      </c>
+      <c r="K98">
+        <v>0.76</v>
+      </c>
+      <c r="L98">
+        <v>1.72</v>
+      </c>
+      <c r="M98">
+        <v>6.2584704</v>
+      </c>
+      <c r="N98">
+        <v>-4.5384704</v>
+      </c>
+      <c r="O98">
+        <v>-1.1346176</v>
+      </c>
+      <c r="P98">
+        <v>-3.4038528</v>
+      </c>
+      <c r="Q98">
+        <v>-2.6438528</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>0.9086172761494755</v>
+      </c>
+      <c r="T98">
+        <v>11.77871361192395</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.0687068840335172</v>
+      </c>
+      <c r="W98">
+        <v>0.2223927960927961</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2748275361340687</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2518417752950633</v>
+      </c>
+      <c r="C99">
+        <v>-20.50674058441369</v>
+      </c>
+      <c r="D99">
+        <v>5.078259415586309</v>
+      </c>
+      <c r="E99">
+        <v>13.081</v>
+      </c>
+      <c r="F99">
+        <v>26.481</v>
+      </c>
+      <c r="G99">
+        <v>0.896</v>
+      </c>
+      <c r="H99">
+        <v>13.9</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>2.48</v>
+      </c>
+      <c r="K99">
+        <v>0.76</v>
+      </c>
+      <c r="L99">
+        <v>1.72</v>
+      </c>
+      <c r="M99">
+        <v>6.323662800000001</v>
+      </c>
+      <c r="N99">
+        <v>-4.603662800000001</v>
+      </c>
+      <c r="O99">
+        <v>-1.1509157</v>
+      </c>
+      <c r="P99">
+        <v>-3.452747100000001</v>
+      </c>
+      <c r="Q99">
+        <v>-2.692747100000001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.198556368199301</v>
+      </c>
+      <c r="T99">
+        <v>15.70495148256526</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.06799856564141907</v>
+      </c>
+      <c r="W99">
+        <v>0.2225619425248291</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2719942625656763</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2538417752950633</v>
+      </c>
+      <c r="C100">
+        <v>-20.82697102983406</v>
+      </c>
+      <c r="D100">
+        <v>5.031028970165941</v>
+      </c>
+      <c r="E100">
+        <v>13.354</v>
+      </c>
+      <c r="F100">
+        <v>26.754</v>
+      </c>
+      <c r="G100">
+        <v>0.896</v>
+      </c>
+      <c r="H100">
+        <v>13.9</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>2.48</v>
+      </c>
+      <c r="K100">
+        <v>0.76</v>
+      </c>
+      <c r="L100">
+        <v>1.72</v>
+      </c>
+      <c r="M100">
+        <v>6.388855200000001</v>
+      </c>
+      <c r="N100">
+        <v>-4.668855200000001</v>
+      </c>
+      <c r="O100">
+        <v>-1.1672138</v>
+      </c>
+      <c r="P100">
+        <v>-3.501641400000001</v>
+      </c>
+      <c r="Q100">
+        <v>-2.741641400000001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>1.778434552298951</v>
+      </c>
+      <c r="T100">
+        <v>23.55742722384789</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.06730470272671071</v>
+      </c>
+      <c r="W100">
+        <v>0.2227276369888615</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2692188109068429</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2558417752950633</v>
+      </c>
+      <c r="C101">
+        <v>-21.14633103553643</v>
+      </c>
+      <c r="D101">
+        <v>4.98466896446357</v>
+      </c>
+      <c r="E101">
+        <v>13.627</v>
+      </c>
+      <c r="F101">
+        <v>27.027</v>
+      </c>
+      <c r="G101">
+        <v>0.896</v>
+      </c>
+      <c r="H101">
+        <v>13.9</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>2.48</v>
+      </c>
+      <c r="K101">
+        <v>0.76</v>
+      </c>
+      <c r="L101">
+        <v>1.72</v>
+      </c>
+      <c r="M101">
+        <v>6.454047600000001</v>
+      </c>
+      <c r="N101">
+        <v>-4.734047600000001</v>
+      </c>
+      <c r="O101">
+        <v>-1.1835119</v>
+      </c>
+      <c r="P101">
+        <v>-3.550535700000001</v>
+      </c>
+      <c r="Q101">
+        <v>-2.790535700000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>3.518069104597902</v>
+      </c>
+      <c r="T101">
+        <v>47.11485444769578</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.06662485724462273</v>
+      </c>
+      <c r="W101">
+        <v>0.2228899840899841</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2664994289784909</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
